--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1914,26 +1914,26 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>bc2088c19862bca8</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Digitador / cajero / auxiliar administrativo / validador documental</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="G31" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-cajero-auxiliar-administrativo-validador-documental-1886745228", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -1960,26 +1960,26 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>9a579fd55998614e</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0.68</v>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="G32" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886764480", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2006,26 +2006,26 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>4490b765a39a686e</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Auxiliar contable - sap - facturacion electronica - bogota</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>0.68</v>
+          <t>ADECCO COLOMBIA S A</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="G33" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-facturacion-electronica-bogota-1886767594", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2052,26 +2052,26 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>7d81d64bbd2753f2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Recepcionista auxiliar de facturación consulta externa</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0.68</v>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="G34" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-auxiliar-de-facturacion-consulta-externa-1886770793", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H34" s="6" t="inlineStr"/>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2098,26 +2098,26 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>975e07c54df5e3db</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>0.68</v>
+          <t>SERO SAS</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="G35" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886771398", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2144,26 +2144,26 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>fae0f941c19be28c</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Auxiliar de facturación urgencias - oficina de facturación</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0.68</v>
+          <t>HUSI</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="G36" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-oficina-de-facturacion-1886766642", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2190,26 +2190,26 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>dbd9c8aa033cf89c</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Auxiliar de facturación urgencias - oficina de facturación</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>0.68</v>
+          <t>HUSI</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="G37" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-oficina-de-facturacion-1886747575", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H37" s="6" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2236,26 +2236,26 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>8f7dd64102e520cd</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0.68</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="G38" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886769035", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2282,26 +2282,26 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>7428ddafa7d405b7</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Auxiliar de Facturación- Remoto</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>0.66</v>
+          <t>NYXN</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="G39" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturaci%C3%B3n-remoto-at-nyxn-4472029589", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H39" s="6" t="inlineStr"/>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2328,7 +2328,7 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2338,16 +2338,16 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0.6</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="G40" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2384,16 +2384,16 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2401,17 +2401,13 @@
         </is>
       </c>
       <c r="G41" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2424,7 +2420,7 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2434,16 +2430,16 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2451,17 +2447,13 @@
         </is>
       </c>
       <c r="G42" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -2474,7 +2466,7 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2484,16 +2476,16 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2501,17 +2493,13 @@
         </is>
       </c>
       <c r="G43" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2524,7 +2512,7 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2534,16 +2522,16 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2551,17 +2539,13 @@
         </is>
       </c>
       <c r="G44" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2574,7 +2558,7 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2584,16 +2568,16 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2601,17 +2585,13 @@
         </is>
       </c>
       <c r="G45" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2624,7 +2604,7 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2634,16 +2614,16 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2651,17 +2631,13 @@
         </is>
       </c>
       <c r="G46" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2674,7 +2650,7 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2684,16 +2660,16 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2701,17 +2677,13 @@
         </is>
       </c>
       <c r="G47" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -2724,26 +2696,26 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2751,17 +2723,13 @@
         </is>
       </c>
       <c r="G48" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2774,26 +2742,26 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -2801,17 +2769,13 @@
         </is>
       </c>
       <c r="G49" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2824,26 +2788,26 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2851,17 +2815,13 @@
         </is>
       </c>
       <c r="G50" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -2874,7 +2834,7 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2884,16 +2844,16 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2901,13 +2861,13 @@
         </is>
       </c>
       <c r="G51" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -2920,7 +2880,7 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2930,16 +2890,16 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2947,13 +2907,13 @@
         </is>
       </c>
       <c r="G52" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2966,7 +2926,7 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2976,12 +2936,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
@@ -2993,10 +2953,14 @@
         </is>
       </c>
       <c r="G53" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H53" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3012,7 +2976,7 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3022,12 +2986,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -3039,10 +3003,14 @@
         </is>
       </c>
       <c r="G54" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H54" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.600.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3058,7 +3026,7 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3068,12 +3036,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
@@ -3085,10 +3053,14 @@
         </is>
       </c>
       <c r="G55" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H55" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3104,7 +3076,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3114,12 +3086,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3131,10 +3103,14 @@
         </is>
       </c>
       <c r="G56" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H56" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3150,7 +3126,7 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3160,12 +3136,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
@@ -3177,10 +3153,14 @@
         </is>
       </c>
       <c r="G57" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H57" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.000.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3196,7 +3176,7 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3206,12 +3186,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3223,10 +3203,14 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H58" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3242,7 +3226,7 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3252,12 +3236,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
@@ -3269,10 +3253,14 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H59" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3288,7 +3276,7 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3298,12 +3286,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3315,10 +3303,14 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H60" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3334,7 +3326,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3344,12 +3336,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3361,10 +3353,14 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H61" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3380,7 +3376,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3390,12 +3386,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3407,10 +3403,14 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H62" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3426,7 +3426,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr"/>
@@ -3472,7 +3472,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
@@ -3610,7 +3610,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3702,7 +3702,7 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr"/>
@@ -3748,7 +3748,7 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
@@ -3840,7 +3840,7 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
@@ -3886,7 +3886,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
@@ -3932,7 +3932,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr"/>
@@ -4208,7 +4208,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4649,13 +4649,13 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4787,13 +4787,13 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4833,13 +4833,13 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5036,7 +5036,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5155,17 +5155,13 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H100" s="6" t="inlineStr"/>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -5178,7 +5174,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5188,16 +5184,16 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5205,17 +5201,13 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H101" s="6" t="inlineStr"/>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5228,52 +5220,1076 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>62e7c31c63a388da</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G102" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H102" s="6" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>6eafefaa9d4e76e6</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Recepcionista facturación en laboratorio clínico</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G103" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H103" s="6" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>1ac2af8aa1b80d19</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Recepcionista facturación en laboratorio clínico</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G104" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H104" s="6" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>5fb21eaeba4e417d</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Siigo</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G105" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H105" s="6" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>acc279cbcc202e8c</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Data Entry Clerk</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Hired</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G106" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H106" s="6" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>c9df64f69713d9c3</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Client Intake and Data Entry Specialist</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Job Duck</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G107" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H107" s="6" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>bfd4f2e4c8eb51d6</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G108" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H108" s="6" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>f71b85e853980a5b</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Booth</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G109" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H109" s="6" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>b124540f32e77f79</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Digitador</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Iron Mountain</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G110" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H110" s="6" t="inlineStr"/>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>648f264595161cd7</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Adecco</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G111" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H111" s="6" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>eb90ed56020b1176</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Inside Sales Contractor</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Credit Wellness, LLC</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G112" s="5">
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>OTE $25k - $35k</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ebabcd51596d0d3b</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable y administrativo</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE ACCOUNTING GROUP</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G113" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>e12bdf1aa280de03</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar administrativo</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G114" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H114" s="6" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>b1fccbf6d15bddc2</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Asistente administrativa</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G115" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H115" s="6" t="inlineStr"/>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>db6a52513ae159ab</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable - sap - bogota</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>ADECCO COLOMBIA S A</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G116" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H116" s="6" t="inlineStr"/>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>ae9358eb43bb2f5b</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable - sap - bogota</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>ADECCO COLOMBIA S A</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G117" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H117" s="6" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>daa8b5315dfb38c2</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable - sap - bogota</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>ADECCO COLOMBIA S A</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G118" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H118" s="6" t="inlineStr"/>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2d35aa26ef7d8409</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Almacenista digitador</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G119" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H119" s="6" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>a36cc8c2293d75bb</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Quirón Prevención Colombia S.A.S</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G120" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H120" s="6" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>e482852a389226cd</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G121" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H121" s="6" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>0dfab7dcd9959d45</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:56</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G122" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H122" s="6" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>bab8c57875b70054</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>HOME BURGERS</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G123" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t>e4553a32da3edf6d</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 16:07</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>SIIGO S.A.S</t>
         </is>
       </c>
-      <c r="E102" s="7" t="n">
+      <c r="E124" s="7" t="n">
         <v>0.53</v>
       </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
-      <c r="G102" s="5">
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G124" s="5">
         <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
-      <c r="H102" s="6" t="inlineStr">
+      <c r="H124" s="6" t="inlineStr">
         <is>
           <t>$ 1.750.905,00 (Mensual)</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I124" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2834,26 +2834,26 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="G51" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2890,16 +2890,16 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2907,13 +2907,13 @@
         </is>
       </c>
       <c r="G52" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2936,16 +2936,16 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2953,17 +2953,13 @@
         </is>
       </c>
       <c r="G53" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -2976,7 +2972,7 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2986,12 +2982,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -3003,12 +2999,12 @@
         </is>
       </c>
       <c r="G54" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -3026,7 +3022,7 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3036,12 +3032,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
@@ -3053,12 +3049,12 @@
         </is>
       </c>
       <c r="G55" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3076,7 +3072,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3086,12 +3082,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="G56" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H56" s="6" t="inlineStr">
@@ -3126,7 +3122,7 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3136,12 +3132,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
@@ -3153,7 +3149,7 @@
         </is>
       </c>
       <c r="G57" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H57" s="6" t="inlineStr">
@@ -3176,7 +3172,7 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3186,12 +3182,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3203,12 +3199,12 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -3226,7 +3222,7 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3236,12 +3232,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
@@ -3253,12 +3249,12 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3276,7 +3272,7 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3286,12 +3282,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3303,12 +3299,12 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.500.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3326,7 +3322,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3353,7 +3349,7 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr">
@@ -3376,7 +3372,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3403,7 +3399,7 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -3426,7 +3422,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3436,12 +3432,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
@@ -3453,10 +3449,14 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H63" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3472,7 +3472,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
@@ -3610,7 +3610,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3702,7 +3702,7 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr"/>
@@ -3748,7 +3748,7 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
@@ -3840,7 +3840,7 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
@@ -3886,7 +3886,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
@@ -3932,7 +3932,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr"/>
@@ -4208,7 +4208,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4668,7 +4668,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4714,7 +4714,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4852,7 +4852,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5036,7 +5036,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5312,7 +5312,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5358,7 +5358,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5404,7 +5404,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5496,7 +5496,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5542,7 +5542,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5588,7 +5588,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5634,7 +5634,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5680,7 +5680,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5707,17 +5707,13 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H112" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H112" s="6" t="inlineStr"/>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -5730,22 +5726,22 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5757,17 +5753,17 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>OTE $25k - $35k</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -5780,7 +5776,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5790,12 +5786,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5807,10 +5803,14 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H114" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -5826,7 +5826,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5872,7 +5872,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
@@ -5918,7 +5918,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
@@ -5964,7 +5964,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6010,7 +6010,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
@@ -6056,7 +6056,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6083,13 +6083,13 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6102,7 +6102,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6148,7 +6148,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
@@ -6194,26 +6194,26 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6221,17 +6221,13 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H123" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6244,52 +6240,424 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>f89540ec077787b1</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar administrativo</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>FUCS</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G124" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H124" s="6" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>abffa88133eaa978</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Almacenista digitador</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G125" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H125" s="6" t="inlineStr"/>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>e4ad43c355211b6e</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Quirón Prevención Colombia S.A.S</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G126" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H126" s="6" t="inlineStr"/>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>ebfb9e3d2b3f916c</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G127" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H127" s="6" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>8478e893d783ed5e</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G128" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>d45621f8599206ec</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>ZEISS Group</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G129" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H129" s="6" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>bab8c57875b70054</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>HOME BURGERS</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G130" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
           <t>e4553a32da3edf6d</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 16:07</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>SIIGO S.A.S</t>
         </is>
       </c>
-      <c r="E124" s="7" t="n">
+      <c r="E131" s="7" t="n">
         <v>0.53</v>
       </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
-      <c r="G124" s="5">
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G131" s="5">
         <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="H131" s="6" t="inlineStr">
         <is>
           <t>$ 1.750.905,00 (Mensual)</t>
         </is>
       </c>
-      <c r="I124" s="3" t="inlineStr">
+      <c r="I131" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G132" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H132" s="6" t="inlineStr"/>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2328,26 +2328,26 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>40e71508f9aac640</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-27 15:43</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar administrativo y contable</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>TRANSINVERLOG SAS</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="G40" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-contable-1886770746", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2374,26 +2374,26 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>cb26be745b2ac668</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-27 15:43</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Profesional en gestión documental- colombia</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="n">
-        <v>0.68</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="G41" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-en-gestion-documental-colombia-1886747593", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2420,26 +2420,26 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>f59b8d03d8d6ee98</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-27 15:43</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Jefe de operaciones gestión documental- colombia</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0.68</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2447,13 +2447,13 @@
         </is>
       </c>
       <c r="G42" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-operaciones-gestion-documental-colombia-1886747595", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2476,16 +2476,16 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="G43" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="G44" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G45" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H45" s="6" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="G46" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
@@ -2650,7 +2650,7 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E47" s="7" t="n">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="G47" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H47" s="6" t="inlineStr"/>
@@ -2696,22 +2696,22 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G48" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H48" s="6" t="inlineStr"/>
@@ -2742,22 +2742,22 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="G49" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H49" s="6" t="inlineStr"/>
@@ -2788,22 +2788,22 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G50" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
@@ -2834,22 +2834,22 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="G51" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
@@ -2880,26 +2880,26 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2907,13 +2907,13 @@
         </is>
       </c>
       <c r="G52" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2926,26 +2926,26 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2953,13 +2953,13 @@
         </is>
       </c>
       <c r="G53" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -2972,26 +2972,26 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2999,17 +2999,13 @@
         </is>
       </c>
       <c r="G54" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3022,7 +3018,7 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3032,16 +3028,16 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3049,17 +3045,13 @@
         </is>
       </c>
       <c r="G55" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3072,7 +3064,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3082,16 +3074,16 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3099,17 +3091,13 @@
         </is>
       </c>
       <c r="G56" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3122,7 +3110,7 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3132,12 +3120,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
@@ -3149,7 +3137,7 @@
         </is>
       </c>
       <c r="G57" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H57" s="6" t="inlineStr">
@@ -3172,7 +3160,7 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3182,12 +3170,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3199,12 +3187,12 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -3222,7 +3210,7 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3232,12 +3220,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
@@ -3249,12 +3237,12 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -3272,7 +3260,7 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3282,12 +3270,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3299,12 +3287,12 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3322,7 +3310,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3332,12 +3320,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3349,12 +3337,12 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3372,7 +3360,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3382,12 +3370,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3399,7 +3387,7 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -3422,7 +3410,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3432,12 +3420,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
@@ -3449,12 +3437,12 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.500.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3472,7 +3460,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3482,12 +3470,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3499,10 +3487,14 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H64" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3518,7 +3510,7 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3528,12 +3520,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3545,10 +3537,14 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H65" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3564,7 +3560,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3574,12 +3570,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3591,10 +3587,14 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H66" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3610,7 +3610,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3702,7 +3702,7 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr"/>
@@ -3748,7 +3748,7 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
@@ -3840,7 +3840,7 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
@@ -3886,7 +3886,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
@@ -3932,7 +3932,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr"/>
@@ -4208,7 +4208,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4668,7 +4668,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4714,7 +4714,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4852,7 +4852,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5036,7 +5036,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5220,7 +5220,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5247,13 +5247,13 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
@@ -5293,13 +5293,13 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5339,13 +5339,13 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -5358,7 +5358,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5404,7 +5404,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5450,7 +5450,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5634,7 +5634,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5680,7 +5680,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
@@ -5726,7 +5726,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5753,17 +5753,13 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H113" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H113" s="6" t="inlineStr"/>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -5776,22 +5772,22 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5803,14 +5799,10 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H114" s="6" t="inlineStr"/>
       <c r="I114" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -5826,22 +5818,22 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5853,7 +5845,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5872,22 +5864,22 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5899,13 +5891,17 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H116" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>OTE $25k - $35k</t>
+        </is>
+      </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -5918,7 +5914,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5928,12 +5924,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -5945,10 +5941,14 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H117" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -5964,7 +5964,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6010,7 +6010,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
@@ -6056,7 +6056,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
@@ -6102,7 +6102,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
@@ -6129,13 +6129,13 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -6148,7 +6148,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6221,13 +6221,13 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6240,22 +6240,22 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6267,13 +6267,13 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6286,17 +6286,17 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -6313,13 +6313,13 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -6332,22 +6332,22 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
@@ -6378,7 +6378,7 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
@@ -6405,13 +6405,13 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6451,13 +6451,13 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -6470,7 +6470,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6497,13 +6497,13 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -6516,26 +6516,26 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -6543,17 +6543,13 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H130" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -6566,26 +6562,26 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -6593,17 +6589,13 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H131" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -6616,7 +6608,7 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6626,16 +6618,16 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -6643,21 +6635,167 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" s="3" t="inlineStr">
         <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>bab8c57875b70054</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>HOME BURGERS</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G133" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>e4553a32da3edf6d</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>SIIGO S.A.S</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G134" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G135" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H135" s="6" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K132" s="3" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2466,26 +2466,26 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>9d08c4fb9804a144</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar facturación hospitalaria</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="G43" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-facturacion-hospitalaria-1886753230", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2512,26 +2512,26 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>00907ef37b1ba1a3</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0.68</v>
+          <t>AGENCIA DE ADUANAS ABC REPECEV S.A. NIVEL I</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2539,13 +2539,13 @@
         </is>
       </c>
       <c r="G44" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886770513", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2558,7 +2558,7 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2568,16 +2568,16 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="G45" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="G46" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
@@ -2650,7 +2650,7 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E47" s="7" t="n">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="G47" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H47" s="6" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G48" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H48" s="6" t="inlineStr"/>
@@ -2742,7 +2742,7 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="G49" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H49" s="6" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G50" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
@@ -2834,22 +2834,22 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="G51" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
@@ -2880,22 +2880,22 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="G52" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="G53" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H53" s="6" t="inlineStr"/>
@@ -2972,22 +2972,22 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="G54" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
@@ -3018,26 +3018,26 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="G55" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3064,26 +3064,26 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="G56" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3110,26 +3110,26 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>62ab67e660127864</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Analista de facturación y cartera</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>DON MAKINON</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3137,17 +3137,13 @@
         </is>
       </c>
       <c r="G57" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3160,7 +3156,7 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3170,16 +3166,16 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3187,17 +3183,13 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3210,7 +3202,7 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3220,16 +3212,16 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3237,17 +3229,13 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3260,7 +3248,7 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3270,12 +3258,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3287,7 +3275,7 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr">
@@ -3310,7 +3298,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3320,12 +3308,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3337,12 +3325,12 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3360,7 +3348,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3370,12 +3358,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3387,12 +3375,12 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3410,7 +3398,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3420,12 +3408,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
@@ -3437,12 +3425,12 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -3460,7 +3448,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3470,12 +3458,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3487,12 +3475,12 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3510,7 +3498,7 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3520,12 +3508,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3537,7 +3525,7 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -3560,7 +3548,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3570,12 +3558,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3587,12 +3575,12 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.500.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3610,7 +3598,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3620,12 +3608,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
@@ -3637,10 +3625,14 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H67" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3656,7 +3648,7 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3666,12 +3658,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3683,10 +3675,14 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H68" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3702,7 +3698,7 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3712,12 +3708,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3729,10 +3725,14 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H69" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3748,7 +3748,7 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
@@ -3840,7 +3840,7 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
@@ -3886,7 +3886,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
@@ -3932,7 +3932,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr"/>
@@ -4208,7 +4208,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4668,7 +4668,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4714,7 +4714,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4852,7 +4852,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5036,7 +5036,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5220,7 +5220,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5312,7 +5312,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5358,7 +5358,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5385,13 +5385,13 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5542,7 +5542,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5588,7 +5588,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5615,13 +5615,13 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -5634,7 +5634,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -5661,13 +5661,13 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
@@ -5772,7 +5772,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
@@ -5818,7 +5818,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5864,7 +5864,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5891,17 +5891,13 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H116" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H116" s="6" t="inlineStr"/>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -5914,22 +5910,22 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -5941,14 +5937,10 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H117" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -5964,22 +5956,22 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -5991,7 +5983,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6010,22 +6002,22 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
@@ -6037,13 +6029,17 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H119" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>OTE $25k - $35k</t>
+        </is>
+      </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6056,7 +6052,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6066,12 +6062,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6083,10 +6079,14 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H120" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6102,7 +6102,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6148,7 +6148,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
@@ -6194,7 +6194,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H123" s="6" t="inlineStr"/>
@@ -6240,7 +6240,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6267,13 +6267,13 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
@@ -6313,13 +6313,13 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6359,13 +6359,13 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -6378,22 +6378,22 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
@@ -6405,13 +6405,13 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6424,17 +6424,17 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -6451,13 +6451,13 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -6470,22 +6470,22 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6543,13 +6543,13 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6572,12 +6572,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
@@ -6589,13 +6589,13 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -6654,26 +6654,26 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -6681,17 +6681,13 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H133" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -6704,26 +6700,26 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -6731,17 +6727,13 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H134" s="6" t="inlineStr"/>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -6754,7 +6746,7 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6764,16 +6756,16 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6773,401 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="3" t="inlineStr">
         <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>6051bd21daa83566</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable y administrativo</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>distrigomez seguros</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G136" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>1a7a81ed9e2a4160</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Universidad Cooperativa de Colombia</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G137" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H137" s="6" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>a81375d5a4201305</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Digitador - bogotá</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>BUREAU VERITAS</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G138" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H138" s="6" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>bab8c57875b70054</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>HOME BURGERS</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G139" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>e4553a32da3edf6d</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>SIIGO S.A.S</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G140" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141" ht="22" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G141" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H141" s="6" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K135" s="3" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G142" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H142" s="6" t="inlineStr"/>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G143" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H143" s="6" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K143"/>
+  <dimension ref="A1:K145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6934,26 +6934,26 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -6961,17 +6961,13 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H139" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H139" s="6" t="inlineStr"/>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -6984,26 +6980,26 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7011,17 +7007,13 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H140" s="6" t="inlineStr"/>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -7034,26 +7026,26 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>bab8c57875b70054</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>HOME BURGERS</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7061,13 +7053,17 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H141" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -7080,26 +7076,26 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>e4553a32da3edf6d</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SIIGO S.A.S</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7107,13 +7103,17 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H142" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -7126,22 +7126,22 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>cd1036bcf66024dc</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Aprendiz practicante administrativo</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>Bold.co</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
@@ -7168,6 +7168,98 @@
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G144" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H144" s="6" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G145" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H145" s="6" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2558,26 +2558,26 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>f380df4133172629</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar de caja y facturación</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>Clinica Barraquer</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="G45" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-caja-y-facturacion-1886773817", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2604,26 +2604,26 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>bb08526620b29a42</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Auxiliar contable y facturación</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>0.68</v>
+          <t>GI GROUP STAFFING S.A.S</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="G46" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-facturacion-1886773695", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2660,16 +2660,16 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="G47" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G48" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H48" s="6" t="inlineStr"/>
@@ -2742,7 +2742,7 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="G49" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H49" s="6" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G50" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
@@ -2834,7 +2834,7 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="G51" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="G52" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -2926,22 +2926,22 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="G53" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H53" s="6" t="inlineStr"/>
@@ -2972,22 +2972,22 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="G54" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="G55" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H55" s="6" t="inlineStr"/>
@@ -3064,22 +3064,22 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="G56" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
@@ -3110,22 +3110,22 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>62ab67e660127864</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y cartera</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>DON MAKINON</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="G57" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H57" s="6" t="inlineStr"/>
@@ -3156,26 +3156,26 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3202,26 +3202,26 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>62ab67e660127864</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Analista de facturación y cartera</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>DON MAKINON</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3248,26 +3248,26 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>39bf6fcb2b2ffb07</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Analista de facturación - medellín</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3275,17 +3275,13 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3298,7 +3294,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3308,16 +3304,16 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3325,17 +3321,13 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3348,7 +3340,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3358,16 +3350,16 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3375,17 +3367,13 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3398,7 +3386,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3408,12 +3396,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
@@ -3425,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -3448,7 +3436,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3458,12 +3446,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3475,12 +3463,12 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3498,7 +3486,7 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3508,12 +3496,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3525,12 +3513,12 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3548,7 +3536,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3558,12 +3546,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3575,12 +3563,12 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3598,7 +3586,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3608,12 +3596,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
@@ -3625,12 +3613,12 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3648,7 +3636,7 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3658,12 +3646,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3675,7 +3663,7 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr">
@@ -3698,7 +3686,7 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3708,12 +3696,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3725,12 +3713,12 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.500.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3748,7 +3736,7 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3758,12 +3746,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3775,10 +3763,14 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H70" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3794,7 +3786,7 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3804,12 +3796,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
@@ -3821,10 +3813,14 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H71" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3840,7 +3836,7 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3850,12 +3846,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3867,10 +3863,14 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H72" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3886,7 +3886,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
@@ -3932,7 +3932,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr"/>
@@ -4208,7 +4208,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4668,7 +4668,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4714,7 +4714,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4852,7 +4852,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5036,7 +5036,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5220,7 +5220,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5312,7 +5312,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5358,7 +5358,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5404,7 +5404,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5450,7 +5450,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5496,7 +5496,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5615,13 +5615,13 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -5634,7 +5634,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5680,7 +5680,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
@@ -5726,7 +5726,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5753,13 +5753,13 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5799,13 +5799,13 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5845,13 +5845,13 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
@@ -5910,7 +5910,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6002,7 +6002,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
@@ -6029,17 +6029,13 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H119" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6052,22 +6048,22 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6079,14 +6075,10 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6102,22 +6094,22 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
@@ -6129,7 +6121,7 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6148,22 +6140,22 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6175,13 +6167,17 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H122" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>OTE $25k - $35k</t>
+        </is>
+      </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -6194,7 +6190,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6204,12 +6200,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6221,10 +6217,14 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H123" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6240,7 +6240,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
@@ -6286,7 +6286,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
@@ -6332,7 +6332,7 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
@@ -6378,7 +6378,7 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
@@ -6405,13 +6405,13 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6451,13 +6451,13 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -6470,7 +6470,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6497,13 +6497,13 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -6516,22 +6516,22 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6543,13 +6543,13 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -6562,17 +6562,17 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -6589,13 +6589,13 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -6608,22 +6608,22 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H132" s="6" t="inlineStr"/>
@@ -6654,7 +6654,7 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
@@ -6681,13 +6681,13 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -6700,7 +6700,7 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H134" s="6" t="inlineStr"/>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -6773,13 +6773,13 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -6792,22 +6792,22 @@
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>6051bd21daa83566</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>distrigomez seguros</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -6819,17 +6819,13 @@
         </is>
       </c>
       <c r="G136" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -6842,22 +6838,22 @@
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>1a7a81ed9e2a4160</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - campus neiva</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Universidad Cooperativa de Colombia</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
@@ -6869,13 +6865,13 @@
         </is>
       </c>
       <c r="G137" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -6888,22 +6884,22 @@
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>a81375d5a4201305</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Digitador - bogotá</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>BUREAU VERITAS</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -6915,7 +6911,7 @@
         </is>
       </c>
       <c r="G138" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H138" s="6" t="inlineStr"/>
@@ -6934,22 +6930,22 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>9164fad20028594e</t>
+          <t>6051bd21daa83566</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Digitador(a) de nómina</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>distrigomez seguros</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
@@ -6961,10 +6957,14 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H139" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6980,22 +6980,22 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>eb9248ba68f06027</t>
+          <t>1a7a81ed9e2a4160</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Universidad Cooperativa de Colombia</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H140" s="6" t="inlineStr"/>
@@ -7026,26 +7026,26 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>a81375d5a4201305</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Digitador - bogotá</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>BUREAU VERITAS</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7053,17 +7053,13 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H141" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H141" s="6" t="inlineStr"/>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -7076,26 +7072,26 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7103,17 +7099,13 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H142" s="6" t="inlineStr"/>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -7126,26 +7118,26 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -7153,13 +7145,13 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -7172,26 +7164,26 @@
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>ab0015399fb0fd5a</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Cali- asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>GERENCIA SELECTA SAS</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -7199,13 +7191,13 @@
         </is>
       </c>
       <c r="G144" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H144" s="6" t="inlineStr"/>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -7218,26 +7210,26 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>f151a5101fd2098d</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Auxiliar contable y administrativo 212747-148845</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -7245,21 +7237,397 @@
         </is>
       </c>
       <c r="G145" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" s="3" t="inlineStr">
         <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2ad924abc5b01201</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:51</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G146" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H146" s="6" t="inlineStr"/>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>cb0d1367aba57052</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:51</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Client Intake and Data Entry Specialist</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Job Duck</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G147" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H147" s="6" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>aa2ff4b012a2356b</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:51</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Data entry specialist</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Naur Talent</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G148" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H148" s="6" t="inlineStr"/>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>bab8c57875b70054</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>HOME BURGERS</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G149" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>e4553a32da3edf6d</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>SIIGO S.A.S</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G150" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151" ht="22" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G151" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H151" s="6" t="inlineStr"/>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G152" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H152" s="6" t="inlineStr"/>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G153" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H153" s="6" t="inlineStr"/>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
+  <dimension ref="A1:K155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2650,26 +2650,26 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>bec3ccae43de3755</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>Méderi</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="G47" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886763059", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2706,16 +2706,16 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2723,13 +2723,13 @@
         </is>
       </c>
       <c r="G48" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="G49" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H49" s="6" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G50" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
@@ -2834,7 +2834,7 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="G51" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="G52" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="G53" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H53" s="6" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="G54" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
@@ -3018,22 +3018,22 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="G55" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H55" s="6" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="G56" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
@@ -3110,7 +3110,7 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="G57" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H57" s="6" t="inlineStr"/>
@@ -3156,22 +3156,22 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
@@ -3202,22 +3202,22 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>62ab67e660127864</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y cartera</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>DON MAKINON</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
@@ -3248,22 +3248,22 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>39bf6fcb2b2ffb07</t>
+          <t>62ab67e660127864</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - medellín</t>
+          <t>Analista de facturación y cartera</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
+          <t>DON MAKINON</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
@@ -3294,26 +3294,26 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>39bf6fcb2b2ffb07</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de facturación - medellín</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3340,7 +3340,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3350,16 +3350,16 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3396,16 +3396,16 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3413,17 +3413,13 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3436,7 +3432,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3446,12 +3442,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3463,12 +3459,12 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -3486,7 +3482,7 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3496,12 +3492,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3513,12 +3509,12 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -3536,7 +3532,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3546,12 +3542,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3563,7 +3559,7 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -3586,7 +3582,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3596,12 +3592,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
@@ -3613,7 +3609,7 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr">
@@ -3636,7 +3632,7 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3646,12 +3642,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3663,12 +3659,12 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -3686,7 +3682,7 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3696,12 +3692,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3713,12 +3709,12 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3736,7 +3732,7 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3746,12 +3742,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3763,12 +3759,12 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.500.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -3786,7 +3782,7 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3813,7 +3809,7 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -3836,7 +3832,7 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3863,7 +3859,7 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr">
@@ -3886,7 +3882,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3896,12 +3892,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3913,10 +3909,14 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H73" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3932,7 +3932,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr"/>
@@ -4208,7 +4208,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4622,7 +4622,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4668,7 +4668,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4714,7 +4714,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4852,7 +4852,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4990,7 +4990,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5036,7 +5036,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5220,7 +5220,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5312,7 +5312,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5358,7 +5358,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5404,7 +5404,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5450,7 +5450,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5496,7 +5496,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5542,7 +5542,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5588,7 +5588,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5634,7 +5634,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -5661,13 +5661,13 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
@@ -5726,7 +5726,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
@@ -5772,7 +5772,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
@@ -5818,7 +5818,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5864,7 +5864,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5891,13 +5891,13 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6002,7 +6002,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
@@ -6048,7 +6048,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
@@ -6094,7 +6094,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6140,7 +6140,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6167,17 +6167,13 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H122" s="6" t="inlineStr"/>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -6190,22 +6186,22 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6217,17 +6213,17 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>OTE $25k - $35k</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6240,7 +6236,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6250,12 +6246,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6267,10 +6263,14 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H124" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6286,7 +6286,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
@@ -6332,7 +6332,7 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
@@ -6378,7 +6378,7 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
@@ -6424,7 +6424,7 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6543,13 +6543,13 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6572,12 +6572,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H132" s="6" t="inlineStr"/>
@@ -6654,22 +6654,22 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
@@ -6681,13 +6681,13 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -6700,7 +6700,7 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H134" s="6" t="inlineStr"/>
@@ -6746,7 +6746,7 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -6773,13 +6773,13 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="G136" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H136" s="6" t="inlineStr"/>
@@ -6838,7 +6838,7 @@
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="G137" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H137" s="6" t="inlineStr"/>
@@ -6884,7 +6884,7 @@
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -6911,13 +6911,13 @@
         </is>
       </c>
       <c r="G138" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H138" s="6" t="inlineStr"/>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -6930,22 +6930,22 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>6051bd21daa83566</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>distrigomez seguros</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
@@ -6957,14 +6957,10 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H139" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H139" s="6" t="inlineStr"/>
       <c r="I139" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6980,7 +6976,7 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>1a7a81ed9e2a4160</t>
+          <t>6051bd21daa83566</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6990,12 +6986,12 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - campus neiva</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Universidad Cooperativa de Colombia</t>
+          <t>distrigomez seguros</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7007,10 +7003,14 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H140" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7026,7 +7026,7 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>a81375d5a4201305</t>
+          <t>1a7a81ed9e2a4160</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Digitador - bogotá</t>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>BUREAU VERITAS</t>
+          <t>Universidad Cooperativa de Colombia</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H141" s="6" t="inlineStr"/>
@@ -7072,22 +7072,22 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>9164fad20028594e</t>
+          <t>a81375d5a4201305</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Digitador(a) de nómina</t>
+          <t>Digitador - bogotá</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>BUREAU VERITAS</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H142" s="6" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>eb9248ba68f06027</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
@@ -7164,22 +7164,22 @@
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>ab0015399fb0fd5a</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Cali- asistente administrativo y contable</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>GERENCIA SELECTA SAS</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="G144" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H144" s="6" t="inlineStr"/>
@@ -7210,7 +7210,7 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>f151a5101fd2098d</t>
+          <t>ab0015399fb0fd5a</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo 212747-148845</t>
+          <t>Cali- asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>GERENCIA SELECTA SAS</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="G145" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H145" s="6" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2ad924abc5b01201</t>
+          <t>f151a5101fd2098d</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
+          <t>Auxiliar contable y administrativo 212747-148845</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="G146" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H146" s="6" t="inlineStr"/>
@@ -7302,7 +7302,7 @@
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>cb0d1367aba57052</t>
+          <t>2ad924abc5b01201</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="G147" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H147" s="6" t="inlineStr"/>
@@ -7348,7 +7348,7 @@
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>aa2ff4b012a2356b</t>
+          <t>cb0d1367aba57052</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Data entry specialist</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Naur Talent</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="G148" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H148" s="6" t="inlineStr"/>
@@ -7394,26 +7394,26 @@
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>aa2ff4b012a2356b</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Data entry specialist</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>Naur Talent</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -7421,17 +7421,13 @@
         </is>
       </c>
       <c r="G149" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H149" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H149" s="6" t="inlineStr"/>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -7444,26 +7440,26 @@
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>0fb7813f6ca58c19</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Data Entry Assistant</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>NEO - New Estate Only</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -7471,17 +7467,13 @@
         </is>
       </c>
       <c r="G150" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H150" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H150" s="6" t="inlineStr"/>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -7494,26 +7486,26 @@
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>bab8c57875b70054</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>HOME BURGERS</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -7521,13 +7513,17 @@
         </is>
       </c>
       <c r="G151" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H151" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -7540,26 +7536,26 @@
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>e4553a32da3edf6d</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SIIGO S.A.S</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -7567,13 +7563,17 @@
         </is>
       </c>
       <c r="G152" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H152" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -7586,22 +7586,22 @@
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>cd1036bcf66024dc</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Aprendiz practicante administrativo</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>Bold.co</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
@@ -7613,7 +7613,7 @@
         </is>
       </c>
       <c r="G153" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H153" s="6" t="inlineStr"/>
@@ -7628,6 +7628,98 @@
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G154" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H154" s="6" t="inlineStr"/>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G155" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H155" s="6" t="inlineStr"/>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:K159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2696,26 +2696,26 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>e960be85369d59ca</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-02 16:41</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar contable y facturación, virtual Teletrabajo</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2723,13 +2723,17 @@
         </is>
       </c>
       <c r="G48" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H48" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-facturacion-virtual-teletrabajo-en-medellin-D3620F133691F6E961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2742,26 +2746,26 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>24da99da017f1199</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-02 16:41</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Auxiliar contable y facturación, virtual Teletrabajo 1626381427-5</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>0.68</v>
+          <t>Colección Talento</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -2769,13 +2773,13 @@
         </is>
       </c>
       <c r="G49" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-y-facturaci%C3%B3n-virtual-teletrabajo-1626381427-5-at-colecci%C3%B3n-talento-4472828244", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2788,26 +2792,26 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>7637d8bf4dbd69d7</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-02 16:41</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Técnico/Tecnólogo en Gestión documental | Agencia de publicidad</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>0.68</v>
+          <t>Omnicom Media Colombia</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2815,13 +2819,13 @@
         </is>
       </c>
       <c r="G50" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-tecn%C3%B3logo-en-gesti%C3%B3n-documental-agencia-de-publicidad-at-omnicom-media-colombia-4461016392", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -2834,26 +2838,26 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>42119fa4e22c5e7b</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-02 16:41</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Auxiliar de Facturación Itagui</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="n">
-        <v>0.68</v>
+          <t>Zeuss S.A.S</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -2861,13 +2865,13 @@
         </is>
       </c>
       <c r="G51" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturaci%C3%B3n-itagui-at-zeuss-s-a-s-4474739314", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -2880,7 +2884,7 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2890,16 +2894,16 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2907,13 +2911,13 @@
         </is>
       </c>
       <c r="G52" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2926,7 +2930,7 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2936,12 +2940,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
@@ -2953,7 +2957,7 @@
         </is>
       </c>
       <c r="G53" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H53" s="6" t="inlineStr"/>
@@ -2972,7 +2976,7 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2982,12 +2986,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2999,7 +3003,7 @@
         </is>
       </c>
       <c r="G54" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
@@ -3018,7 +3022,7 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3028,12 +3032,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
@@ -3045,7 +3049,7 @@
         </is>
       </c>
       <c r="G55" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H55" s="6" t="inlineStr"/>
@@ -3064,12 +3068,12 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3079,7 +3083,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3091,7 +3095,7 @@
         </is>
       </c>
       <c r="G56" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
@@ -3110,22 +3114,22 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
@@ -3137,7 +3141,7 @@
         </is>
       </c>
       <c r="G57" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H57" s="6" t="inlineStr"/>
@@ -3156,22 +3160,22 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3183,7 +3187,7 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
@@ -3202,22 +3206,22 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
@@ -3229,7 +3233,7 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
@@ -3248,22 +3252,22 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>62ab67e660127864</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y cartera</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>DON MAKINON</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3275,7 +3279,7 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
@@ -3294,22 +3298,22 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>39bf6fcb2b2ffb07</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - medellín</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3321,7 +3325,7 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr"/>
@@ -3340,26 +3344,26 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3367,13 +3371,13 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3386,26 +3390,26 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3413,13 +3417,13 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3432,26 +3436,26 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>62ab67e660127864</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Analista de facturación y cartera</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>DON MAKINON</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3459,17 +3463,13 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3482,26 +3482,26 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>39bf6fcb2b2ffb07</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Analista de facturación - medellín</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3509,17 +3509,13 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H65" s="6" t="inlineStr"/>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3532,7 +3528,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3542,16 +3538,16 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3559,17 +3555,13 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -3582,7 +3574,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3592,16 +3584,16 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3609,17 +3601,13 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3632,7 +3620,7 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3642,12 +3630,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3659,7 +3647,7 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr">
@@ -3682,7 +3670,7 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3692,12 +3680,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3709,12 +3697,12 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -3732,7 +3720,7 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3742,12 +3730,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3759,12 +3747,12 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -3782,7 +3770,7 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3792,12 +3780,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
@@ -3809,12 +3797,12 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -3832,7 +3820,7 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3842,12 +3830,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3859,12 +3847,12 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -3882,7 +3870,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3892,12 +3880,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3909,7 +3897,7 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr">
@@ -3932,7 +3920,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3942,12 +3930,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3959,10 +3947,14 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H74" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -3978,7 +3970,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3988,12 +3980,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -4005,10 +3997,14 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H75" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4024,7 +4020,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4034,12 +4030,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4051,10 +4047,14 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H76" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4070,7 +4070,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4097,10 +4097,14 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H77" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4116,7 +4120,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4126,12 +4130,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4143,7 +4147,7 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr"/>
@@ -4162,7 +4166,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4172,7 +4176,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -4189,7 +4193,7 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr"/>
@@ -4208,7 +4212,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4218,7 +4222,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -4235,7 +4239,7 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
@@ -4254,7 +4258,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4264,12 +4268,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4281,7 +4285,7 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -4300,7 +4304,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4310,12 +4314,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4327,7 +4331,7 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr"/>
@@ -4346,7 +4350,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4356,7 +4360,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -4373,7 +4377,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr"/>
@@ -4392,7 +4396,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4402,12 +4406,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4419,7 +4423,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
@@ -4438,7 +4442,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4448,12 +4452,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4465,7 +4469,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4484,7 +4488,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4494,12 +4498,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4511,7 +4515,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4530,7 +4534,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4540,12 +4544,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4557,7 +4561,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4576,7 +4580,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4586,12 +4590,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4603,7 +4607,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4622,7 +4626,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4632,12 +4636,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4649,7 +4653,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4668,7 +4672,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4678,12 +4682,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4695,7 +4699,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4714,7 +4718,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4724,12 +4728,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4741,7 +4745,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4760,7 +4764,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4770,12 +4774,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4787,7 +4791,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4806,7 +4810,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4816,12 +4820,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4833,7 +4837,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4852,7 +4856,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4862,12 +4866,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4879,7 +4883,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4898,7 +4902,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4908,12 +4912,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4925,7 +4929,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4944,7 +4948,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4954,12 +4958,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4971,7 +4975,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4990,7 +4994,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5000,12 +5004,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5017,7 +5021,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5036,7 +5040,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5046,12 +5050,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5063,7 +5067,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5082,7 +5086,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5092,12 +5096,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5109,7 +5113,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5128,7 +5132,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5138,12 +5142,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5155,7 +5159,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5174,7 +5178,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5184,12 +5188,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5201,7 +5205,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5220,7 +5224,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5230,7 +5234,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -5247,7 +5251,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5266,7 +5270,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5276,7 +5280,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -5293,7 +5297,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5312,7 +5316,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5322,12 +5326,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5339,7 +5343,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5358,7 +5362,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5368,12 +5372,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5385,7 +5389,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5404,7 +5408,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5414,7 +5418,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -5431,7 +5435,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5450,7 +5454,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5460,7 +5464,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -5477,7 +5481,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5496,7 +5500,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5506,12 +5510,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5523,7 +5527,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5542,7 +5546,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5552,12 +5556,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5569,7 +5573,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5588,7 +5592,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5598,7 +5602,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -5615,7 +5619,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5634,7 +5638,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5644,12 +5648,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -5661,7 +5665,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5680,7 +5684,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5690,12 +5694,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5707,13 +5711,13 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -5726,7 +5730,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5736,12 +5740,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5753,13 +5757,13 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -5772,7 +5776,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5782,12 +5786,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5799,13 +5803,13 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -5818,7 +5822,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5828,12 +5832,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5845,13 +5849,13 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -5864,7 +5868,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5874,12 +5878,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5891,7 +5895,7 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
@@ -5910,7 +5914,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5920,12 +5924,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -5937,13 +5941,13 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -5956,7 +5960,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5966,12 +5970,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -5983,13 +5987,13 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6002,7 +6006,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6012,12 +6016,12 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
@@ -6029,13 +6033,13 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6048,7 +6052,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6058,12 +6062,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6075,13 +6079,13 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6094,7 +6098,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6104,12 +6108,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
@@ -6121,7 +6125,7 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6140,7 +6144,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6150,12 +6154,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6167,7 +6171,7 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
@@ -6186,7 +6190,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6196,12 +6200,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6213,17 +6217,13 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H123" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6236,22 +6236,22 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6263,14 +6263,10 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6286,22 +6282,22 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
@@ -6313,7 +6309,7 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
@@ -6332,22 +6328,22 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6359,7 +6355,7 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
@@ -6378,22 +6374,22 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
@@ -6405,13 +6401,17 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H127" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>OTE $25k - $35k</t>
+        </is>
+      </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6451,10 +6451,14 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H128" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6470,7 +6474,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6480,12 +6484,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6497,7 +6501,7 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
@@ -6516,7 +6520,7 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6526,12 +6530,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6543,7 +6547,7 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
@@ -6562,7 +6566,7 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6572,12 +6576,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
@@ -6589,13 +6593,13 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -6608,7 +6612,7 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6618,12 +6622,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6635,13 +6639,13 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -6654,7 +6658,7 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6664,12 +6668,12 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
@@ -6681,13 +6685,13 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -6700,22 +6704,22 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6727,7 +6731,7 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H134" s="6" t="inlineStr"/>
@@ -6746,22 +6750,22 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -6773,13 +6777,13 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -6792,22 +6796,22 @@
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -6819,7 +6823,7 @@
         </is>
       </c>
       <c r="G136" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H136" s="6" t="inlineStr"/>
@@ -6838,12 +6842,12 @@
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -6865,7 +6869,7 @@
         </is>
       </c>
       <c r="G137" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H137" s="6" t="inlineStr"/>
@@ -6884,7 +6888,7 @@
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6894,12 +6898,12 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -6911,13 +6915,13 @@
         </is>
       </c>
       <c r="G138" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H138" s="6" t="inlineStr"/>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -6930,7 +6934,7 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6940,12 +6944,12 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
@@ -6957,7 +6961,7 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H139" s="6" t="inlineStr"/>
@@ -6976,22 +6980,22 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>6051bd21daa83566</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>distrigomez seguros</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7003,17 +7007,13 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H140" s="6" t="inlineStr"/>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -7026,22 +7026,22 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>1a7a81ed9e2a4160</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - campus neiva</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Universidad Cooperativa de Colombia</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
@@ -7053,13 +7053,13 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H141" s="6" t="inlineStr"/>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -7072,22 +7072,22 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>a81375d5a4201305</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Digitador - bogotá</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>BUREAU VERITAS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7099,13 +7099,13 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H142" s="6" t="inlineStr"/>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>9164fad20028594e</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Digitador(a) de nómina</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
@@ -7164,22 +7164,22 @@
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>eb9248ba68f06027</t>
+          <t>6051bd21daa83566</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>distrigomez seguros</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7191,10 +7191,14 @@
         </is>
       </c>
       <c r="G144" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H144" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7210,22 +7214,22 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>ab0015399fb0fd5a</t>
+          <t>1a7a81ed9e2a4160</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Cali- asistente administrativo y contable</t>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>GERENCIA SELECTA SAS</t>
+          <t>Universidad Cooperativa de Colombia</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
@@ -7237,7 +7241,7 @@
         </is>
       </c>
       <c r="G145" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H145" s="6" t="inlineStr"/>
@@ -7256,22 +7260,22 @@
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>f151a5101fd2098d</t>
+          <t>a81375d5a4201305</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo 212747-148845</t>
+          <t>Digitador - bogotá</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>BUREAU VERITAS</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7283,7 +7287,7 @@
         </is>
       </c>
       <c r="G146" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H146" s="6" t="inlineStr"/>
@@ -7302,22 +7306,22 @@
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>2ad924abc5b01201</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
@@ -7329,7 +7333,7 @@
         </is>
       </c>
       <c r="G147" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H147" s="6" t="inlineStr"/>
@@ -7348,22 +7352,22 @@
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>cb0d1367aba57052</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7375,7 +7379,7 @@
         </is>
       </c>
       <c r="G148" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H148" s="6" t="inlineStr"/>
@@ -7394,7 +7398,7 @@
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>aa2ff4b012a2356b</t>
+          <t>ab0015399fb0fd5a</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7404,12 +7408,12 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Data entry specialist</t>
+          <t>Cali- asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Naur Talent</t>
+          <t>GERENCIA SELECTA SAS</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
@@ -7421,7 +7425,7 @@
         </is>
       </c>
       <c r="G149" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H149" s="6" t="inlineStr"/>
@@ -7440,22 +7444,22 @@
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>0fb7813f6ca58c19</t>
+          <t>f151a5101fd2098d</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Assistant</t>
+          <t>Auxiliar contable y administrativo 212747-148845</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>NEO - New Estate Only</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7467,7 +7471,7 @@
         </is>
       </c>
       <c r="G150" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H150" s="6" t="inlineStr"/>
@@ -7486,26 +7490,26 @@
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>2ad924abc5b01201</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -7513,17 +7517,13 @@
         </is>
       </c>
       <c r="G151" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H151" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H151" s="6" t="inlineStr"/>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -7536,26 +7536,26 @@
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>cb0d1367aba57052</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -7563,17 +7563,13 @@
         </is>
       </c>
       <c r="G152" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H152" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H152" s="6" t="inlineStr"/>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -7586,26 +7582,26 @@
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>aa2ff4b012a2356b</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Data entry specialist</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>Naur Talent</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -7613,13 +7609,13 @@
         </is>
       </c>
       <c r="G153" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H153" s="6" t="inlineStr"/>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -7632,26 +7628,26 @@
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>0fb7813f6ca58c19</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Data Entry Assistant</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>NEO - New Estate Only</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -7659,13 +7655,13 @@
         </is>
       </c>
       <c r="G154" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H154" s="6" t="inlineStr"/>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -7678,48 +7674,240 @@
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>bab8c57875b70054</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>HOME BURGERS</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G155" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156" ht="22" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>e4553a32da3edf6d</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>SIIGO S.A.S</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G156" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G157" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H157" s="6" t="inlineStr"/>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G158" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H158" s="6" t="inlineStr"/>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159" ht="22" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
           <t>550ad8afea6faf9b</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 18:38</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>Auxiliar Contable Junior</t>
         </is>
       </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>Ariadna Communications Group</t>
         </is>
       </c>
-      <c r="E155" s="7" t="n">
+      <c r="E159" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
-      <c r="G155" s="5">
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G159" s="5">
         <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
         <v/>
       </c>
-      <c r="H155" s="6" t="inlineStr"/>
-      <c r="I155" s="3" t="inlineStr">
+      <c r="H159" s="6" t="inlineStr"/>
+      <c r="I159" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K155" s="3" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -668,26 +668,26 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>5e69bdc3d8d68672</t>
+          <t>3c78d827079503ad</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Facturación Teletrabajo</t>
+          <t>Digitador SAP</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>Industrias Puropollo S.A.S</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -695,17 +695,13 @@
         </is>
       </c>
       <c r="G4" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-de-facturacion-teletrabajo-en-cali-436F39785C023D1261373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-sap-at-industrias-puropollo-s-a-s-4475052500", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 78/100 - Alta Afinidad] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -718,7 +714,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>7cf82a12d60b65c7</t>
+          <t>5e69bdc3d8d68672</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -728,12 +724,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable- conocimiento y dominio en erp siigo nube</t>
+          <t>Auxiliar de Facturación Teletrabajo</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -745,10 +741,14 @@
         </is>
       </c>
       <c r="G5" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-conocimiento-y-dominio-en-erp-siigo-nube-1886749387", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-de-facturacion-teletrabajo-en-cali-436F39785C023D1261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -764,7 +764,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>80dcaff6c76c4739</t>
+          <t>7cf82a12d60b65c7</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Auxiliar contable- conocimiento y dominio en erp siigo nube</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Tower Consulting WorldWide SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="G6" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886756116", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-conocimiento-y-dominio-en-erp-siigo-nube-1886749387", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
@@ -810,7 +810,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2a5b492f2cf08a86</t>
+          <t>80dcaff6c76c4739</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion // yopal medio tiempo</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Tower Consulting WorldWide SAS</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G7" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-yopal-medio-tiempo-1886767206", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886756116", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
@@ -856,7 +856,7 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>4e81a6e21cf2499c</t>
+          <t>2a5b492f2cf08a86</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - facturacion electronica - bogota</t>
+          <t>Auxiliar de facturacion // yopal medio tiempo</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="G8" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-facturacion-electronica-bogota-1886767171", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-yopal-medio-tiempo-1886767206", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="inlineStr"/>
@@ -902,7 +902,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>5b72a870b18cd8dd</t>
+          <t>4e81a6e21cf2499c</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Auxiliar contable - sap - facturacion electronica - bogota</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="G9" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886767351", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-facturacion-electronica-bogota-1886767171", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="inlineStr"/>
@@ -948,7 +948,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>aaf3a1241a43d56a</t>
+          <t>5b72a870b18cd8dd</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Asistente de facturación y despachos - yumbo</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>DISAN COLOMBIA S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="G10" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-facturacion-y-despachos-yumbo-1886765290", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886767351", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="inlineStr"/>
@@ -994,7 +994,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>4c6e2ae68998ff1f</t>
+          <t>aaf3a1241a43d56a</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Asistente de facturación y despachos - yumbo</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>DISAN COLOMBIA S.A.S</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="G11" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-ibague-1886770122", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-facturacion-y-despachos-yumbo-1886765290", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
@@ -1040,7 +1040,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>dad6a39f05eb0872</t>
+          <t>4c6e2ae68998ff1f</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación hospitalario</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>INSTITUTO ROOSEVELT</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="G12" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalario-1886760993", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-ibague-1886770122", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H12" s="6" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>c80879dace821f2d</t>
+          <t>dad6a39f05eb0872</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación - 1626343701-25</t>
+          <t>Auxiliar de facturación hospitalario</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>INSTITUTO ROOSEVELT</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="G13" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-162634370125-1886768889", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalario-1886760993", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>a581954268b43f5e</t>
+          <t>c80879dace821f2d</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion hospitalaria</t>
+          <t>Auxiliar de facturación - 1626343701-25</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="G14" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalaria-1886760847", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-162634370125-1886768889", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>f19945acad64eb39</t>
+          <t>a581954268b43f5e</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>CLINICA SHAIO</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="G15" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalaria-1886377445", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalaria-1886760847", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>c5b127601236be94</t>
+          <t>f19945acad64eb39</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion // sector salud laboratorio clinico /// villavicencio meta</t>
+          <t>Auxiliar de facturacion hospitalaria</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CLINICA SHAIO</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="G16" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-sector-salud-laboratorio-clinico-villavicencio-meta-1886746288", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalaria-1886377445", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>6bf2402aaa779ade</t>
+          <t>c5b127601236be94</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>1626506410-20 - auxiliar de facturación - engativá</t>
+          <t>Auxiliar de facturacion // sector salud laboratorio clinico /// villavicencio meta</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="G17" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/162650641020-auxiliar-de-facturacion-engativa-1886768147", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-sector-salud-laboratorio-clinico-villavicencio-meta-1886746288", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H17" s="6" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>9211ddea62d9bfb6</t>
+          <t>6bf2402aaa779ade</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación experiencia en armado y radicación de cuentas</t>
+          <t>1626506410-20 - auxiliar de facturación - engativá</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="G18" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-experiencia-en-armado-y-radicacion-de-cuentas-1886744224", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/162650641020-auxiliar-de-facturacion-engativa-1886768147", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1525a4a624cf5cd3</t>
+          <t>9211ddea62d9bfb6</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion cuentas medicas indefinido</t>
+          <t>Auxiliar de facturación experiencia en armado y radicación de cuentas</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="G19" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-cuentas-medicas-indefinido-1886767336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-experiencia-en-armado-y-radicacion-de-cuentas-1886744224", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
@@ -1408,7 +1408,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>d24c0581ada3f712</t>
+          <t>1525a4a624cf5cd3</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista auxiliar de facturación área laboratorio clínico</t>
+          <t>Auxiliar de facturacion cuentas medicas indefinido</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="G20" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-auxiliar-de-facturacion-area-laboratorio-clinico-1886771966", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-cuentas-medicas-indefinido-1886767336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H20" s="6" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>fb3dea6d6d65b76e</t>
+          <t>d24c0581ada3f712</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion conocimientos en sap</t>
+          <t>Recepcionista auxiliar de facturación área laboratorio clínico</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>ATIEMPO S.A.S</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="G21" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-conocimientos-en-sap-1886753956", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-auxiliar-de-facturacion-area-laboratorio-clinico-1886771966", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>88175481acb2458e</t>
+          <t>fb3dea6d6d65b76e</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y facturacion</t>
+          <t>Auxiliar de facturacion conocimientos en sap</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ATIEMPO S.A.S</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="G22" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-facturacion-1886744516", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-conocimientos-en-sap-1886753956", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H22" s="6" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>d82065ac5307df49</t>
+          <t>88175481acb2458e</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Asistente contable y facturacion</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="G23" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886758187", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-facturacion-1886744516", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H23" s="6" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>25faa90c6ef28e21</t>
+          <t>d82065ac5307df49</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación e inventarios</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Human construction sas</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="G24" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-e-inventarios-1886756606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886758187", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>a40cdd7efd6dc67a</t>
+          <t>25faa90c6ef28e21</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación urgencias / hospitalizacion</t>
+          <t>Auxiliar de facturación e inventarios</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Human construction sas</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="G25" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-hospitalizacion-1886752826", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-e-inventarios-1886756606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H25" s="6" t="inlineStr"/>
@@ -1684,7 +1684,7 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>72196b37f0710891</t>
+          <t>a40cdd7efd6dc67a</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Asistente de operaciones y facturación</t>
+          <t>Auxiliar de facturación urgencias / hospitalizacion</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="G26" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-operaciones-y-facturacion-1886763278", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-hospitalizacion-1886752826", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H26" s="6" t="inlineStr"/>
@@ -1730,7 +1730,7 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>aa68d537158b69c9</t>
+          <t>72196b37f0710891</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Asistente de operaciones y facturación</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G27" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886760972", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-operaciones-y-facturacion-1886763278", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
@@ -1776,7 +1776,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>32a63b8bbac24a30</t>
+          <t>aa68d537158b69c9</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Facturación - Área Financiera</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Philippi Prietocarrizosa Ferrero DU &amp; Uria</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="G28" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturaci%C3%B3n-%C3%A1rea-financiera-at-philippi-prietocarrizosa-ferrero-du-uria-4460252170", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886760972", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H28" s="6" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>368b286993a892d4</t>
+          <t>32a63b8bbac24a30</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar regional de facturación y recaudo</t>
+          <t>Auxiliar de Facturación - Área Financiera</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Interaseo S.A.S. E.S.P.</t>
+          <t>Philippi Prietocarrizosa Ferrero DU &amp; Uria</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="G29" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-regional-de-facturaci%C3%B3n-y-recaudo-at-interaseo-s-a-s-e-s-p-4471161048", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturaci%C3%B3n-%C3%A1rea-financiera-at-philippi-prietocarrizosa-ferrero-du-uria-4460252170", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H29" s="6" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>80916d693f0f0430</t>
+          <t>368b286993a892d4</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Facturacion y Cartera</t>
+          <t>Auxiliar regional de facturación y recaudo</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Interaseo S.A.S. E.S.P.</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="G30" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturacion-y-cartera-at-eurofins-4454827077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-regional-de-facturaci%C3%B3n-y-recaudo-at-interaseo-s-a-s-e-s-p-4471161048", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H30" s="6" t="inlineStr"/>
@@ -1914,22 +1914,22 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>bc2088c19862bca8</t>
+          <t>80916d693f0f0430</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Digitador / cajero / auxiliar administrativo / validador documental</t>
+          <t>Auxiliar de Facturacion y Cartera</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="G31" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-cajero-auxiliar-administrativo-validador-documental-1886745228", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturacion-y-cartera-at-eurofins-4454827077", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>9a579fd55998614e</t>
+          <t>bc2088c19862bca8</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Digitador / cajero / auxiliar administrativo / validador documental</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="G32" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886764480", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-cajero-auxiliar-administrativo-validador-documental-1886745228", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>4490b765a39a686e</t>
+          <t>9a579fd55998614e</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - facturacion electronica - bogota</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="G33" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-facturacion-electronica-bogota-1886767594", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886764480", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H33" s="6" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>7d81d64bbd2753f2</t>
+          <t>4490b765a39a686e</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista auxiliar de facturación consulta externa</t>
+          <t>Auxiliar contable - sap - facturacion electronica - bogota</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="G34" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-auxiliar-de-facturacion-consulta-externa-1886770793", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-facturacion-electronica-bogota-1886767594", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H34" s="6" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>975e07c54df5e3db</t>
+          <t>7d81d64bbd2753f2</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Recepcionista auxiliar de facturación consulta externa</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>SERO SAS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="G35" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886771398", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-auxiliar-de-facturacion-consulta-externa-1886770793", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H35" s="6" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>fae0f941c19be28c</t>
+          <t>975e07c54df5e3db</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación urgencias - oficina de facturación</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>HUSI</t>
+          <t>SERO SAS</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="G36" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-oficina-de-facturacion-1886766642", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886771398", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2190,7 +2190,7 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>dbd9c8aa033cf89c</t>
+          <t>fae0f941c19be28c</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G37" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-oficina-de-facturacion-1886747575", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-oficina-de-facturacion-1886766642", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H37" s="6" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>8f7dd64102e520cd</t>
+          <t>dbd9c8aa033cf89c</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Auxiliar de facturación urgencias - oficina de facturación</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>HUSI</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="G38" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886769035", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-oficina-de-facturacion-1886747575", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>7428ddafa7d405b7</t>
+          <t>8f7dd64102e520cd</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Facturación- Remoto</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>NYXN</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="G39" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturaci%C3%B3n-remoto-at-nyxn-4472029589", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886769035", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H39" s="6" t="inlineStr"/>
@@ -2328,22 +2328,22 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>40e71508f9aac640</t>
+          <t>7428ddafa7d405b7</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:43</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y contable</t>
+          <t>Auxiliar de Facturación- Remoto</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>TRANSINVERLOG SAS</t>
+          <t>NYXN</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -2355,13 +2355,13 @@
         </is>
       </c>
       <c r="G40" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-contable-1886770746", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturaci%C3%B3n-remoto-at-nyxn-4472029589", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>cb26be745b2ac668</t>
+          <t>40e71508f9aac640</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Profesional en gestión documental- colombia</t>
+          <t>Auxiliar administrativo y contable</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>TRANSINVERLOG SAS</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="G41" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-en-gestion-documental-colombia-1886747593", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-contable-1886770746", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H41" s="6" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>f59b8d03d8d6ee98</t>
+          <t>cb26be745b2ac668</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Jefe de operaciones gestión documental- colombia</t>
+          <t>Profesional en gestión documental- colombia</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="G42" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-operaciones-gestion-documental-colombia-1886747595", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/profesional-en-gestion-documental-colombia-1886747593", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H42" s="6" t="inlineStr"/>
@@ -2466,22 +2466,22 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>9d08c4fb9804a144</t>
+          <t>f59b8d03d8d6ee98</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-27 15:43</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar facturación hospitalaria</t>
+          <t>Jefe de operaciones gestión documental- colombia</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="G43" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-facturacion-hospitalaria-1886753230", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/jefe-de-operaciones-gestion-documental-colombia-1886747595", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>00907ef37b1ba1a3</t>
+          <t>9d08c4fb9804a144</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Auxiliar facturación hospitalaria</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE ADUANAS ABC REPECEV S.A. NIVEL I</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="G44" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886770513", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-facturacion-hospitalaria-1886753230", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
@@ -2558,22 +2558,22 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>f380df4133172629</t>
+          <t>00907ef37b1ba1a3</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de caja y facturación</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Clinica Barraquer</t>
+          <t>AGENCIA DE ADUANAS ABC REPECEV S.A. NIVEL I</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G45" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-caja-y-facturacion-1886773817", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886770513", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H45" s="6" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>bb08526620b29a42</t>
+          <t>f380df4133172629</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y facturación</t>
+          <t>Auxiliar de caja y facturación</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>GI GROUP STAFFING S.A.S</t>
+          <t>Clinica Barraquer</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="G46" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-facturacion-1886773695", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-caja-y-facturacion-1886773817", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
@@ -2650,22 +2650,22 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>bec3ccae43de3755</t>
+          <t>bb08526620b29a42</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Auxiliar contable y facturación</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Méderi</t>
+          <t>GI GROUP STAFFING S.A.S</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="G47" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886763059", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-facturacion-1886773695", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H47" s="6" t="inlineStr"/>
@@ -2696,22 +2696,22 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>e960be85369d59ca</t>
+          <t>bec3ccae43de3755</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:41</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y facturación, virtual Teletrabajo</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>Méderi</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -2723,14 +2723,10 @@
         </is>
       </c>
       <c r="G48" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-facturacion-virtual-teletrabajo-en-medellin-D3620F133691F6E961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886763059", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -2746,7 +2742,7 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>24da99da017f1199</t>
+          <t>e960be85369d59ca</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2756,12 +2752,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y facturación, virtual Teletrabajo 1626381427-5</t>
+          <t>Auxiliar contable y facturación, virtual Teletrabajo</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Colección Talento</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -2773,10 +2769,14 @@
         </is>
       </c>
       <c r="G49" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-y-facturaci%C3%B3n-virtual-teletrabajo-1626381427-5-at-colecci%C3%B3n-talento-4472828244", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H49" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-facturacion-virtual-teletrabajo-en-medellin-D3620F133691F6E961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -2792,7 +2792,7 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>7637d8bf4dbd69d7</t>
+          <t>24da99da017f1199</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Técnico/Tecnólogo en Gestión documental | Agencia de publicidad</t>
+          <t>Auxiliar contable y facturación, virtual Teletrabajo 1626381427-5</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Omnicom Media Colombia</t>
+          <t>Colección Talento</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="G50" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-tecn%C3%B3logo-en-gesti%C3%B3n-documental-agencia-de-publicidad-at-omnicom-media-colombia-4461016392", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-y-facturaci%C3%B3n-virtual-teletrabajo-1626381427-5-at-colecci%C3%B3n-talento-4472828244", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>42119fa4e22c5e7b</t>
+          <t>7637d8bf4dbd69d7</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Facturación Itagui</t>
+          <t>Técnico/Tecnólogo en Gestión documental | Agencia de publicidad</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Zeuss S.A.S</t>
+          <t>Omnicom Media Colombia</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
@@ -2865,13 +2865,13 @@
         </is>
       </c>
       <c r="G51" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturaci%C3%B3n-itagui-at-zeuss-s-a-s-4474739314", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/t%C3%A9cnico-tecn%C3%B3logo-en-gesti%C3%B3n-documental-agencia-de-publicidad-at-omnicom-media-colombia-4461016392", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -2884,26 +2884,26 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>42119fa4e22c5e7b</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-02 16:41</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar de Facturación Itagui</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>Zeuss S.A.S</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2911,13 +2911,13 @@
         </is>
       </c>
       <c r="G52" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-facturaci%C3%B3n-itagui-at-zeuss-s-a-s-4474739314", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2930,26 +2930,26 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>bfccc78523bd9bce</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Auxiliar de facturación - 1626011292-16</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>0.68</v>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="G53" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-162601129216-1886771083", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -2976,26 +2976,26 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>62b2ee56724184dc</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>0.68</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="G54" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886774943", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3022,26 +3022,26 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>cce37295998e85f3</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Auxiliar de facturación experiencia en rips</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="n">
-        <v>0.68</v>
+          <t>Fundación Santa Fe de Bogotá</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3049,13 +3049,13 @@
         </is>
       </c>
       <c r="G55" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-experiencia-en-rips-1886775772", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3068,26 +3068,26 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>dfa58446a2372fcc</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Asistente de facturación y cartera ref. 1626487352-32</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>0.68</v>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3095,13 +3095,13 @@
         </is>
       </c>
       <c r="G56" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-facturacion-y-cartera-ref-162648735232-1886766205", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3124,16 +3124,16 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="G57" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
@@ -3206,7 +3206,7 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
@@ -3252,17 +3252,17 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
@@ -3298,22 +3298,22 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr"/>
@@ -3344,22 +3344,22 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
@@ -3390,22 +3390,22 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr"/>
@@ -3436,22 +3436,22 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>62ab67e660127864</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y cartera</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>DON MAKINON</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
@@ -3482,22 +3482,22 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>39bf6fcb2b2ffb07</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - medellín</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
@@ -3528,26 +3528,26 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -3574,26 +3574,26 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3620,26 +3620,26 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -3647,17 +3647,13 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -3670,26 +3666,26 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>62ab67e660127864</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Analista de facturación y cartera</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>DON MAKINON</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -3697,17 +3693,13 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -3720,26 +3712,26 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>39bf6fcb2b2ffb07</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Analista de facturación - medellín</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -3747,17 +3739,13 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -3770,7 +3758,7 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3780,16 +3768,16 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -3797,17 +3785,13 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H71" s="6" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -3820,7 +3804,7 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3830,16 +3814,16 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -3847,17 +3831,13 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -3870,7 +3850,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3880,12 +3860,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3897,12 +3877,12 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -3920,7 +3900,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3930,12 +3910,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3947,12 +3927,12 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -3970,7 +3950,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3980,12 +3960,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -3997,12 +3977,12 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4020,7 +4000,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4030,12 +4010,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4047,12 +4027,12 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4070,7 +4050,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4080,12 +4060,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4097,12 +4077,12 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4120,7 +4100,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4130,12 +4110,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4147,10 +4127,14 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H78" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4166,7 +4150,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4176,12 +4160,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4193,10 +4177,14 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H79" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4212,7 +4200,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4222,12 +4210,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4239,10 +4227,14 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H80" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4258,7 +4250,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4268,12 +4260,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4285,10 +4277,14 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H81" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4304,7 +4300,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4314,12 +4310,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4331,10 +4327,14 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H82" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4350,7 +4350,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr"/>
@@ -4396,7 +4396,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
@@ -4442,7 +4442,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4488,7 +4488,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4580,7 +4580,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4590,12 +4590,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4626,7 +4626,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4672,7 +4672,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4856,7 +4856,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4902,7 +4902,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5086,7 +5086,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5362,7 +5362,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5408,7 +5408,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5454,7 +5454,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5500,7 +5500,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5592,7 +5592,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5638,7 +5638,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
@@ -5776,7 +5776,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -5987,13 +5987,13 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6052,7 +6052,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6079,13 +6079,13 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -6144,7 +6144,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
@@ -6401,17 +6401,13 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6424,22 +6420,22 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6451,14 +6447,10 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6474,22 +6466,22 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6501,7 +6493,7 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
@@ -6520,22 +6512,22 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6547,7 +6539,7 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
@@ -6566,22 +6558,22 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
@@ -6593,7 +6585,7 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
@@ -6612,22 +6604,22 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6639,13 +6631,17 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H132" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>OTE $25k - $35k</t>
+        </is>
+      </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -6658,7 +6654,7 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6668,12 +6664,12 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
@@ -6685,10 +6681,14 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H133" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6704,7 +6704,7 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H134" s="6" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -6777,13 +6777,13 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -6823,13 +6823,13 @@
         </is>
       </c>
       <c r="G136" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
@@ -6869,13 +6869,13 @@
         </is>
       </c>
       <c r="G137" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -6888,22 +6888,22 @@
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G138" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H138" s="6" t="inlineStr"/>
@@ -6934,12 +6934,12 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H139" s="6" t="inlineStr"/>
@@ -6980,12 +6980,12 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H140" s="6" t="inlineStr"/>
@@ -7026,22 +7026,22 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H141" s="6" t="inlineStr"/>
@@ -7072,17 +7072,17 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H142" s="6" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
@@ -7164,22 +7164,22 @@
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>6051bd21daa83566</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>distrigomez seguros</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7191,14 +7191,10 @@
         </is>
       </c>
       <c r="G144" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H144" s="6" t="inlineStr"/>
       <c r="I144" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7214,22 +7210,22 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>1a7a81ed9e2a4160</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - campus neiva</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Universidad Cooperativa de Colombia</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
@@ -7241,13 +7237,13 @@
         </is>
       </c>
       <c r="G145" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -7260,22 +7256,22 @@
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>a81375d5a4201305</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Digitador - bogotá</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>BUREAU VERITAS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7287,13 +7283,13 @@
         </is>
       </c>
       <c r="G146" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -7306,22 +7302,22 @@
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>9164fad20028594e</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Digitador(a) de nómina</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
@@ -7333,13 +7329,13 @@
         </is>
       </c>
       <c r="G147" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H147" s="6" t="inlineStr"/>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -7352,22 +7348,22 @@
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>eb9248ba68f06027</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7379,7 +7375,7 @@
         </is>
       </c>
       <c r="G148" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H148" s="6" t="inlineStr"/>
@@ -7398,22 +7394,22 @@
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>ab0015399fb0fd5a</t>
+          <t>6051bd21daa83566</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Cali- asistente administrativo y contable</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>GERENCIA SELECTA SAS</t>
+          <t>distrigomez seguros</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
@@ -7425,10 +7421,14 @@
         </is>
       </c>
       <c r="G149" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H149" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7444,22 +7444,22 @@
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>f151a5101fd2098d</t>
+          <t>1a7a81ed9e2a4160</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo 212747-148845</t>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Universidad Cooperativa de Colombia</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7471,7 +7471,7 @@
         </is>
       </c>
       <c r="G150" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H150" s="6" t="inlineStr"/>
@@ -7490,22 +7490,22 @@
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>2ad924abc5b01201</t>
+          <t>a81375d5a4201305</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
+          <t>Digitador - bogotá</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>BUREAU VERITAS</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G151" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H151" s="6" t="inlineStr"/>
@@ -7536,22 +7536,22 @@
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>cb0d1367aba57052</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="G152" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H152" s="6" t="inlineStr"/>
@@ -7582,22 +7582,22 @@
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>aa2ff4b012a2356b</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Data entry specialist</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Naur Talent</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="G153" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H153" s="6" t="inlineStr"/>
@@ -7628,22 +7628,22 @@
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>0fb7813f6ca58c19</t>
+          <t>ab0015399fb0fd5a</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Assistant</t>
+          <t>Cali- asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>NEO - New Estate Only</t>
+          <t>GERENCIA SELECTA SAS</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="G154" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H154" s="6" t="inlineStr"/>
@@ -7674,26 +7674,26 @@
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>f151a5101fd2098d</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Auxiliar contable y administrativo 212747-148845</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -7701,17 +7701,13 @@
         </is>
       </c>
       <c r="G155" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H155" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -7724,26 +7720,26 @@
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>2ad924abc5b01201</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -7751,17 +7747,13 @@
         </is>
       </c>
       <c r="G156" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H156" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H156" s="6" t="inlineStr"/>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -7774,26 +7766,26 @@
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>cb0d1367aba57052</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -7801,13 +7793,13 @@
         </is>
       </c>
       <c r="G157" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H157" s="6" t="inlineStr"/>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -7820,26 +7812,26 @@
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>aa2ff4b012a2356b</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Data entry specialist</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Naur Talent</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -7847,13 +7839,13 @@
         </is>
       </c>
       <c r="G158" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H158" s="6" t="inlineStr"/>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -7866,26 +7858,26 @@
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>0fb7813f6ca58c19</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Data Entry Assistant</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>NEO - New Estate Only</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -7893,21 +7885,405 @@
         </is>
       </c>
       <c r="G159" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H159" s="6" t="inlineStr"/>
       <c r="I159" s="3" t="inlineStr">
         <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>e03aa4c6959d3eb4</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:14</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G160" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>1a638820869677f4</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:14</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Asistente administrativa</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Valgroup Realty LLC</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G161" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162" ht="22" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>bab8c57875b70054</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>HOME BURGERS</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G162" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>e4553a32da3edf6d</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>SIIGO S.A.S</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G163" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>838f39602895a4e7</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:14</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>MANPOWER</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Hibrido</t>
+        </is>
+      </c>
+      <c r="G164" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H164" s="6" t="inlineStr"/>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G165" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H165" s="6" t="inlineStr"/>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K159" s="3" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G166" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H166" s="6" t="inlineStr"/>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167" ht="22" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G167" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H167" s="6" t="inlineStr"/>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3114,26 +3114,26 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>aa44c6d913e4d552</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-04 15:51</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar de facturación - puente aranda- 1625881713-123</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="G57" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-puente-aranda-1625881713123-1886769348", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3170,16 +3170,16 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3187,13 +3187,13 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
@@ -3252,7 +3252,7 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
@@ -3298,7 +3298,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
@@ -3482,22 +3482,22 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
@@ -3620,22 +3620,22 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3666,22 +3666,22 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>62ab67e660127864</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y cartera</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>DON MAKINON</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr"/>
@@ -3712,22 +3712,22 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>39bf6fcb2b2ffb07</t>
+          <t>62ab67e660127864</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - medellín</t>
+          <t>Analista de facturación y cartera</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
+          <t>DON MAKINON</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3758,26 +3758,26 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>39bf6fcb2b2ffb07</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de facturación - medellín</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3814,16 +3814,16 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3860,16 +3860,16 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -3877,17 +3877,13 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -3900,7 +3896,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3910,12 +3906,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3927,12 +3923,12 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -3950,7 +3946,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3960,12 +3956,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -3977,12 +3973,12 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -4000,7 +3996,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4010,12 +4006,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4027,7 +4023,7 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -4050,7 +4046,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4060,12 +4056,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4077,7 +4073,7 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -4100,7 +4096,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4110,12 +4106,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4127,12 +4123,12 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4150,7 +4146,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4160,12 +4156,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4177,12 +4173,12 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4200,7 +4196,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4210,12 +4206,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4227,12 +4223,12 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.500.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4250,7 +4246,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4277,7 +4273,7 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -4300,7 +4296,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4327,7 +4323,7 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr">
@@ -4350,7 +4346,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4360,12 +4356,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4377,10 +4373,14 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H83" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4396,7 +4396,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr"/>
@@ -4442,7 +4442,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4488,7 +4488,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4580,7 +4580,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4626,7 +4626,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4672,7 +4672,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4856,7 +4856,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4902,7 +4902,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5086,7 +5086,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5362,7 +5362,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5408,7 +5408,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5454,7 +5454,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5500,7 +5500,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5592,7 +5592,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5638,7 +5638,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
@@ -5776,7 +5776,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
@@ -5960,7 +5960,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
@@ -6052,7 +6052,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -6144,7 +6144,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
@@ -6190,7 +6190,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H123" s="6" t="inlineStr"/>
@@ -6236,7 +6236,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
@@ -6282,7 +6282,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
@@ -6328,7 +6328,7 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
@@ -6420,7 +6420,7 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
@@ -6466,7 +6466,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
@@ -6512,7 +6512,7 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
@@ -6558,7 +6558,7 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
@@ -6604,7 +6604,7 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6631,17 +6631,13 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -6654,22 +6650,22 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
@@ -6681,17 +6677,17 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>OTE $25k - $35k</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -6704,7 +6700,7 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6714,12 +6710,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6731,10 +6727,14 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H134" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6750,7 +6750,7 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H135" s="6" t="inlineStr"/>
@@ -6796,7 +6796,7 @@
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G136" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H136" s="6" t="inlineStr"/>
@@ -6842,7 +6842,7 @@
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G137" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H137" s="6" t="inlineStr"/>
@@ -6888,7 +6888,7 @@
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G138" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H138" s="6" t="inlineStr"/>
@@ -6934,7 +6934,7 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H139" s="6" t="inlineStr"/>
@@ -6980,7 +6980,7 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7007,13 +7007,13 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H140" s="6" t="inlineStr"/>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H141" s="6" t="inlineStr"/>
@@ -7072,7 +7072,7 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H142" s="6" t="inlineStr"/>
@@ -7118,22 +7118,22 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
@@ -7145,13 +7145,13 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="G144" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H144" s="6" t="inlineStr"/>
@@ -7210,7 +7210,7 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="G145" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="G146" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H146" s="6" t="inlineStr"/>
@@ -7302,7 +7302,7 @@
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="G147" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H147" s="6" t="inlineStr"/>
@@ -7348,7 +7348,7 @@
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7375,13 +7375,13 @@
         </is>
       </c>
       <c r="G148" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H148" s="6" t="inlineStr"/>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -7394,22 +7394,22 @@
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>6051bd21daa83566</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>distrigomez seguros</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
@@ -7421,14 +7421,10 @@
         </is>
       </c>
       <c r="G149" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H149" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H149" s="6" t="inlineStr"/>
       <c r="I149" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7444,7 +7440,7 @@
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>1a7a81ed9e2a4160</t>
+          <t>6051bd21daa83566</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7454,12 +7450,12 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - campus neiva</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Universidad Cooperativa de Colombia</t>
+          <t>distrigomez seguros</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7471,10 +7467,14 @@
         </is>
       </c>
       <c r="G150" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H150" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7490,7 +7490,7 @@
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>a81375d5a4201305</t>
+          <t>1a7a81ed9e2a4160</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Digitador - bogotá</t>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>BUREAU VERITAS</t>
+          <t>Universidad Cooperativa de Colombia</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G151" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H151" s="6" t="inlineStr"/>
@@ -7536,22 +7536,22 @@
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>9164fad20028594e</t>
+          <t>a81375d5a4201305</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Digitador(a) de nómina</t>
+          <t>Digitador - bogotá</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>BUREAU VERITAS</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="G152" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H152" s="6" t="inlineStr"/>
@@ -7582,7 +7582,7 @@
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>eb9248ba68f06027</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="G153" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H153" s="6" t="inlineStr"/>
@@ -7628,22 +7628,22 @@
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ab0015399fb0fd5a</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Cali- asistente administrativo y contable</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>GERENCIA SELECTA SAS</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="G154" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H154" s="6" t="inlineStr"/>
@@ -7674,7 +7674,7 @@
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>f151a5101fd2098d</t>
+          <t>ab0015399fb0fd5a</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -7684,12 +7684,12 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo 212747-148845</t>
+          <t>Cali- asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>GERENCIA SELECTA SAS</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="G155" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H155" s="6" t="inlineStr"/>
@@ -7720,7 +7720,7 @@
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2ad924abc5b01201</t>
+          <t>f151a5101fd2098d</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
+          <t>Auxiliar contable y administrativo 212747-148845</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="G156" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H156" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>cb0d1367aba57052</t>
+          <t>2ad924abc5b01201</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G157" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H157" s="6" t="inlineStr"/>
@@ -7812,7 +7812,7 @@
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>aa2ff4b012a2356b</t>
+          <t>cb0d1367aba57052</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Data entry specialist</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Naur Talent</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="G158" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H158" s="6" t="inlineStr"/>
@@ -7858,22 +7858,22 @@
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>0fb7813f6ca58c19</t>
+          <t>aa2ff4b012a2356b</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Assistant</t>
+          <t>Data entry specialist</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>NEO - New Estate Only</t>
+          <t>Naur Talent</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="G159" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H159" s="6" t="inlineStr"/>
@@ -7904,22 +7904,22 @@
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>e03aa4c6959d3eb4</t>
+          <t>0fb7813f6ca58c19</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Data Entry Assistant</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>NEO - New Estate Only</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7931,14 +7931,10 @@
         </is>
       </c>
       <c r="G160" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H160" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H160" s="6" t="inlineStr"/>
       <c r="I160" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7954,7 +7950,7 @@
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>1a638820869677f4</t>
+          <t>e03aa4c6959d3eb4</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -7964,12 +7960,12 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Valgroup Realty LLC</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
@@ -7981,7 +7977,7 @@
         </is>
       </c>
       <c r="G161" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H161" s="6" t="inlineStr">
@@ -8004,26 +8000,26 @@
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>1a638820869677f4</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>Valgroup Realty LLC</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -8031,17 +8027,17 @@
         </is>
       </c>
       <c r="G162" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -8054,7 +8050,7 @@
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>bab8c57875b70054</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8064,12 +8060,12 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>HOME BURGERS</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
@@ -8081,12 +8077,12 @@
         </is>
       </c>
       <c r="G163" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H163" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>$ 1.750.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -8104,22 +8100,22 @@
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>838f39602895a4e7</t>
+          <t>e4553a32da3edf6d</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>SIIGO S.A.S</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8127,17 +8123,21 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Hibrido</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="G164" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H164" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -8150,40 +8150,40 @@
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>838f39602895a4e7</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>Hibrido</t>
         </is>
       </c>
       <c r="G165" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H165" s="6" t="inlineStr"/>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -8196,22 +8196,22 @@
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>cd1036bcf66024dc</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Aprendiz practicante administrativo</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Bold.co</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="G166" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H166" s="6" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>dbdce1eb16060a6a</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Auxiliar contable jr</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
@@ -8269,7 +8269,7 @@
         </is>
       </c>
       <c r="G167" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H167" s="6" t="inlineStr"/>
@@ -8284,6 +8284,52 @@
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168" ht="22" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G168" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H168" s="6" t="inlineStr"/>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K168"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8050,26 +8050,26 @@
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>d310964f2dc8e97e</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-05 19:48</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Aprendiz sena - auxiliar de servicio al cliente y ventas digitales remoto</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>M&amp;S VITAMINS SAS</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -8077,17 +8077,13 @@
         </is>
       </c>
       <c r="G163" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aprendiz-sena-auxiliar-de-servicio-al-cliente-y-ventas-digitales-remoto-1886776017", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H163" s="6" t="inlineStr"/>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -8100,26 +8096,26 @@
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>feadb7d6306993cf</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-05 19:48</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -8127,17 +8123,13 @@
         </is>
       </c>
       <c r="G164" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886776241", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H164" s="6" t="inlineStr"/>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -8150,22 +8142,22 @@
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>838f39602895a4e7</t>
+          <t>bab8c57875b70054</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>HOME BURGERS</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
@@ -8173,17 +8165,21 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Hibrido</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="G165" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H165" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -8196,26 +8192,26 @@
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>e4553a32da3edf6d</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>SIIGO S.A.S</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -8223,13 +8219,17 @@
         </is>
       </c>
       <c r="G166" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H166" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -8242,40 +8242,40 @@
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>838f39602895a4e7</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>Hibrido</t>
         </is>
       </c>
       <c r="G167" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H167" s="6" t="inlineStr"/>
       <c r="I167" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -8288,22 +8288,22 @@
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>cd1036bcf66024dc</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Aprendiz practicante administrativo</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>Bold.co</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="G168" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H168" s="6" t="inlineStr"/>
@@ -8330,6 +8330,98 @@
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169" ht="22" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G169" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H169" s="6" t="inlineStr"/>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr"/>
+    </row>
+    <row r="170" ht="22" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G170" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H170" s="6" t="inlineStr"/>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K170"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3804,26 +3804,26 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>65f969075798969c</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de facturación en salud</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-en-salud-1886772546", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3860,16 +3860,16 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3906,16 +3906,16 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -3923,17 +3923,13 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -3946,7 +3942,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3956,12 +3952,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
@@ -3973,12 +3969,12 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -3996,7 +3992,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4006,12 +4002,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4023,12 +4019,12 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4046,7 +4042,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4056,12 +4052,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4073,7 +4069,7 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -4096,7 +4092,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4106,12 +4102,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4123,7 +4119,7 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -4146,7 +4142,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4156,12 +4152,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4173,12 +4169,12 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4196,7 +4192,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4206,12 +4202,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4223,12 +4219,12 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4246,7 +4242,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4256,12 +4252,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4273,12 +4269,12 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.500.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4296,7 +4292,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4323,7 +4319,7 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr">
@@ -4346,7 +4342,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4373,7 +4369,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -4396,7 +4392,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4406,12 +4402,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4423,10 +4419,14 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H84" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4442,7 +4442,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr"/>
@@ -4488,7 +4488,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4580,7 +4580,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4590,12 +4590,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4626,7 +4626,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4672,7 +4672,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4856,7 +4856,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4902,7 +4902,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5086,7 +5086,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5362,7 +5362,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5408,7 +5408,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5454,7 +5454,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5500,7 +5500,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5592,7 +5592,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5638,7 +5638,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
@@ -5776,7 +5776,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
@@ -5960,7 +5960,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
@@ -6052,7 +6052,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6144,7 +6144,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H123" s="6" t="inlineStr"/>
@@ -6236,7 +6236,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
@@ -6282,7 +6282,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
@@ -6328,7 +6328,7 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
@@ -6401,13 +6401,13 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6420,7 +6420,7 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
@@ -6466,7 +6466,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
@@ -6512,7 +6512,7 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
@@ -6558,7 +6558,7 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
@@ -6604,7 +6604,7 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H132" s="6" t="inlineStr"/>
@@ -6650,7 +6650,7 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
@@ -6677,17 +6677,13 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H133" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -6700,22 +6696,22 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6727,17 +6723,17 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>OTE $25k - $35k</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -6750,7 +6746,7 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6760,12 +6756,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -6777,10 +6773,14 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H135" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6796,7 +6796,7 @@
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G136" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H136" s="6" t="inlineStr"/>
@@ -6842,7 +6842,7 @@
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G137" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H137" s="6" t="inlineStr"/>
@@ -6888,7 +6888,7 @@
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G138" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H138" s="6" t="inlineStr"/>
@@ -6934,7 +6934,7 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H139" s="6" t="inlineStr"/>
@@ -6980,7 +6980,7 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H140" s="6" t="inlineStr"/>
@@ -7026,7 +7026,7 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
@@ -7053,13 +7053,13 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H141" s="6" t="inlineStr"/>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H142" s="6" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
@@ -7164,22 +7164,22 @@
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7191,13 +7191,13 @@
         </is>
       </c>
       <c r="G144" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H144" s="6" t="inlineStr"/>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="G145" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H145" s="6" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="G146" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="G147" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H147" s="6" t="inlineStr"/>
@@ -7348,7 +7348,7 @@
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="G148" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H148" s="6" t="inlineStr"/>
@@ -7394,7 +7394,7 @@
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
@@ -7421,13 +7421,13 @@
         </is>
       </c>
       <c r="G149" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H149" s="6" t="inlineStr"/>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -7440,22 +7440,22 @@
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>6051bd21daa83566</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>distrigomez seguros</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7467,14 +7467,10 @@
         </is>
       </c>
       <c r="G150" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H150" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H150" s="6" t="inlineStr"/>
       <c r="I150" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7490,7 +7486,7 @@
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>1a7a81ed9e2a4160</t>
+          <t>6051bd21daa83566</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7500,12 +7496,12 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - campus neiva</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Universidad Cooperativa de Colombia</t>
+          <t>distrigomez seguros</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
@@ -7517,10 +7513,14 @@
         </is>
       </c>
       <c r="G151" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H151" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7536,7 +7536,7 @@
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>a81375d5a4201305</t>
+          <t>1a7a81ed9e2a4160</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7546,12 +7546,12 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Digitador - bogotá</t>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>BUREAU VERITAS</t>
+          <t>Universidad Cooperativa de Colombia</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="G152" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H152" s="6" t="inlineStr"/>
@@ -7582,22 +7582,22 @@
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>9164fad20028594e</t>
+          <t>a81375d5a4201305</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Digitador(a) de nómina</t>
+          <t>Digitador - bogotá</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>BUREAU VERITAS</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="G153" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H153" s="6" t="inlineStr"/>
@@ -7628,7 +7628,7 @@
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>eb9248ba68f06027</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="G154" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H154" s="6" t="inlineStr"/>
@@ -7674,22 +7674,22 @@
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>ab0015399fb0fd5a</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Cali- asistente administrativo y contable</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>GERENCIA SELECTA SAS</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="G155" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H155" s="6" t="inlineStr"/>
@@ -7720,7 +7720,7 @@
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>f151a5101fd2098d</t>
+          <t>ab0015399fb0fd5a</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo 212747-148845</t>
+          <t>Cali- asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>GERENCIA SELECTA SAS</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="G156" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H156" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>2ad924abc5b01201</t>
+          <t>f151a5101fd2098d</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
+          <t>Auxiliar contable y administrativo 212747-148845</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G157" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H157" s="6" t="inlineStr"/>
@@ -7812,7 +7812,7 @@
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>cb0d1367aba57052</t>
+          <t>2ad924abc5b01201</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="G158" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H158" s="6" t="inlineStr"/>
@@ -7858,7 +7858,7 @@
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>aa2ff4b012a2356b</t>
+          <t>cb0d1367aba57052</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Data entry specialist</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Naur Talent</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="G159" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H159" s="6" t="inlineStr"/>
@@ -7904,22 +7904,22 @@
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>0fb7813f6ca58c19</t>
+          <t>aa2ff4b012a2356b</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Assistant</t>
+          <t>Data entry specialist</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>NEO - New Estate Only</t>
+          <t>Naur Talent</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="G160" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H160" s="6" t="inlineStr"/>
@@ -7950,22 +7950,22 @@
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>e03aa4c6959d3eb4</t>
+          <t>0fb7813f6ca58c19</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Data Entry Assistant</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>NEO - New Estate Only</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
@@ -7977,14 +7977,10 @@
         </is>
       </c>
       <c r="G161" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H161" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H161" s="6" t="inlineStr"/>
       <c r="I161" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8000,7 +7996,7 @@
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>1a638820869677f4</t>
+          <t>e03aa4c6959d3eb4</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8010,12 +8006,12 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Valgroup Realty LLC</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8027,7 +8023,7 @@
         </is>
       </c>
       <c r="G162" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H162" s="6" t="inlineStr">
@@ -8050,22 +8046,22 @@
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>d310964f2dc8e97e</t>
+          <t>1a638820869677f4</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:48</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz sena - auxiliar de servicio al cliente y ventas digitales remoto</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>M&amp;S VITAMINS SAS</t>
+          <t>Valgroup Realty LLC</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
@@ -8077,10 +8073,14 @@
         </is>
       </c>
       <c r="G163" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aprendiz-sena-auxiliar-de-servicio-al-cliente-y-ventas-digitales-remoto-1886776017", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H163" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8096,7 +8096,7 @@
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>feadb7d6306993cf</t>
+          <t>d310964f2dc8e97e</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Aprendiz sena - auxiliar de servicio al cliente y ventas digitales remoto</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>M&amp;S VITAMINS SAS</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="G164" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886776241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aprendiz-sena-auxiliar-de-servicio-al-cliente-y-ventas-digitales-remoto-1886776017", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H164" s="6" t="inlineStr"/>
@@ -8142,26 +8142,26 @@
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>feadb7d6306993cf</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-05 19:48</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -8169,17 +8169,13 @@
         </is>
       </c>
       <c r="G165" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H165" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886776241", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H165" s="6" t="inlineStr"/>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -8192,26 +8188,26 @@
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>6dae76f41229d9ff</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Auxiliar Administrativo desde casa</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>POLITÉCNICO INTERNACIONAL DE OCCIDENTE</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -8219,17 +8215,17 @@
         </is>
       </c>
       <c r="G166" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-desde-casa-personal-con-discapacidad-en-bogota-dc-5A794030AFDA0F8661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -8242,40 +8238,40 @@
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>838f39602895a4e7</t>
+          <t>d59b1a44f5bebbdc</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>TALENT SPEAKERS COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Hibrido</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="G167" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-1886775760", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H167" s="6" t="inlineStr"/>
       <c r="I167" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -8288,26 +8284,26 @@
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>bab8c57875b70054</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>HOME BURGERS</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -8315,13 +8311,17 @@
         </is>
       </c>
       <c r="G168" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H168" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8334,26 +8334,26 @@
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>e4553a32da3edf6d</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SIIGO S.A.S</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -8361,13 +8361,17 @@
         </is>
       </c>
       <c r="G169" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H169" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -8380,48 +8384,232 @@
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>838f39602895a4e7</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>Hibrido</t>
         </is>
       </c>
       <c r="G170" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H170" s="6" t="inlineStr"/>
       <c r="I170" s="3" t="inlineStr">
         <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr"/>
+    </row>
+    <row r="171" ht="22" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>c2dea1f07ef53647</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:14</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>TALYCAP GLOBAL SAS</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G171" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H171" s="6" t="inlineStr"/>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172" ht="22" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G172" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H172" s="6" t="inlineStr"/>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K170" s="3" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G173" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H173" s="6" t="inlineStr"/>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G174" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H174" s="6" t="inlineStr"/>
+      <c r="I174" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:K177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8284,26 +8284,26 @@
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>594e79b4cd7df756</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-07 17:52</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Auxiliar administrativo - contable y operativo</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>EFICACIA S.A.S</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -8311,17 +8311,13 @@
         </is>
       </c>
       <c r="G168" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H168" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-contable-y-operativo-1886776165", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H168" s="6" t="inlineStr"/>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8334,26 +8330,26 @@
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>30c827aff6e8bff7</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-07 17:52</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>INDI Staffing Services</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -8361,17 +8357,13 @@
         </is>
       </c>
       <c r="G169" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H169" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-remote-work-at-indi-staffing-services-4476714759", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H169" s="6" t="inlineStr"/>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -8384,22 +8376,22 @@
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>838f39602895a4e7</t>
+          <t>bab8c57875b70054</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>HOME BURGERS</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8407,17 +8399,21 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Hibrido</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="G170" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H170" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -8430,22 +8426,22 @@
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>c2dea1f07ef53647</t>
+          <t>e4553a32da3edf6d</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>SIIGO S.A.S</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
@@ -8457,10 +8453,14 @@
         </is>
       </c>
       <c r="G171" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H171" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8476,40 +8476,40 @@
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>838f39602895a4e7</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>Hibrido</t>
         </is>
       </c>
       <c r="G172" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H172" s="6" t="inlineStr"/>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -8522,26 +8522,26 @@
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>c2dea1f07ef53647</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>TALYCAP GLOBAL SAS</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -8549,13 +8549,13 @@
         </is>
       </c>
       <c r="G173" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H173" s="6" t="inlineStr"/>
       <c r="I173" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -8568,48 +8568,190 @@
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
+          <t>d55c5bcc13a598dc</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:52</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Asesor(a) de servicio al cliente bilingüe</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Empresa en expansión</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G174" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesora-de-servicio-al-cliente-bilingue-home-office-ingles-c1-con-experiencia-en-estados-unidos-D522AAAB4F954B8061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.500.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G175" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H175" s="6" t="inlineStr"/>
+      <c r="I175" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr"/>
+    </row>
+    <row r="176" ht="22" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G176" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H176" s="6" t="inlineStr"/>
+      <c r="I176" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr"/>
+    </row>
+    <row r="177" ht="22" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
           <t>550ad8afea6faf9b</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 18:38</t>
         </is>
       </c>
-      <c r="C174" s="3" t="inlineStr">
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t>Auxiliar Contable Junior</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>Ariadna Communications Group</t>
         </is>
       </c>
-      <c r="E174" s="7" t="n">
+      <c r="E177" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
-      <c r="G174" s="5">
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G177" s="5">
         <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
         <v/>
       </c>
-      <c r="H174" s="6" t="inlineStr"/>
-      <c r="I174" s="3" t="inlineStr">
+      <c r="H177" s="6" t="inlineStr"/>
+      <c r="I177" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K174" s="3" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K177"/>
+  <dimension ref="A1:K185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3160,26 +3160,26 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>b44601c704ec6932</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar de facturación control de fletes y sobrecostos</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3187,13 +3187,13 @@
         </is>
       </c>
       <c r="G58" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-control-de-fletes-y-sobrecostos-1886778160", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3216,16 +3216,16 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3233,13 +3233,13 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
@@ -3298,7 +3298,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
@@ -3528,22 +3528,22 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3666,22 +3666,22 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr"/>
@@ -3712,22 +3712,22 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>62ab67e660127864</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y cartera</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>DON MAKINON</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3758,22 +3758,22 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>39bf6fcb2b2ffb07</t>
+          <t>62ab67e660127864</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - medellín</t>
+          <t>Analista de facturación y cartera</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
+          <t>DON MAKINON</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
@@ -3804,22 +3804,22 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>65f969075798969c</t>
+          <t>39bf6fcb2b2ffb07</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación en salud</t>
+          <t>Analista de facturación - medellín</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-en-salud-1886772546", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
@@ -3850,26 +3850,26 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>65f969075798969c</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de facturación en salud</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-en-salud-1886772546", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3906,16 +3906,16 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3952,16 +3952,16 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -3969,17 +3969,13 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -3992,7 +3988,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4002,12 +3998,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4019,12 +4015,12 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -4042,7 +4038,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4052,12 +4048,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4069,12 +4065,12 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4092,7 +4088,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4102,12 +4098,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4119,7 +4115,7 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -4142,7 +4138,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4152,12 +4148,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4169,7 +4165,7 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr">
@@ -4192,7 +4188,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4202,12 +4198,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4219,12 +4215,12 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4242,7 +4238,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4252,12 +4248,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4269,12 +4265,12 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4292,7 +4288,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4302,12 +4298,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4319,12 +4315,12 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.500.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4342,7 +4338,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4369,7 +4365,7 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -4392,7 +4388,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4419,7 +4415,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -4442,7 +4438,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4452,12 +4448,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4469,10 +4465,14 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H85" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4488,7 +4488,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4580,7 +4580,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4590,12 +4590,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4626,7 +4626,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4672,7 +4672,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4856,7 +4856,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4902,7 +4902,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5086,7 +5086,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5362,7 +5362,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5408,7 +5408,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5454,7 +5454,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5500,7 +5500,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5592,7 +5592,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5638,7 +5638,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
@@ -5776,7 +5776,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
@@ -5960,7 +5960,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
@@ -6052,7 +6052,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6144,7 +6144,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
@@ -6190,7 +6190,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
@@ -6282,7 +6282,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
@@ -6328,7 +6328,7 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
@@ -6420,7 +6420,7 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -6466,7 +6466,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
@@ -6512,7 +6512,7 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
@@ -6558,7 +6558,7 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
@@ -6604,7 +6604,7 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H132" s="6" t="inlineStr"/>
@@ -6650,7 +6650,7 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H133" s="6" t="inlineStr"/>
@@ -6696,7 +6696,7 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6723,17 +6723,13 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H134" s="6" t="inlineStr"/>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -6746,22 +6742,22 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -6773,17 +6769,17 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>OTE $25k - $35k</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -6796,7 +6792,7 @@
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6806,12 +6802,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -6823,10 +6819,14 @@
         </is>
       </c>
       <c r="G136" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H136" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6842,7 +6842,7 @@
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G137" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H137" s="6" t="inlineStr"/>
@@ -6888,7 +6888,7 @@
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G138" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H138" s="6" t="inlineStr"/>
@@ -6934,7 +6934,7 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H139" s="6" t="inlineStr"/>
@@ -6980,7 +6980,7 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H140" s="6" t="inlineStr"/>
@@ -7026,7 +7026,7 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H141" s="6" t="inlineStr"/>
@@ -7072,7 +7072,7 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7099,13 +7099,13 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H142" s="6" t="inlineStr"/>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
@@ -7164,7 +7164,7 @@
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="G144" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H144" s="6" t="inlineStr"/>
@@ -7210,22 +7210,22 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="G145" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="G146" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H146" s="6" t="inlineStr"/>
@@ -7302,7 +7302,7 @@
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
@@ -7329,13 +7329,13 @@
         </is>
       </c>
       <c r="G147" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H147" s="6" t="inlineStr"/>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -7348,7 +7348,7 @@
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="G148" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H148" s="6" t="inlineStr"/>
@@ -7394,7 +7394,7 @@
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="G149" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H149" s="6" t="inlineStr"/>
@@ -7440,7 +7440,7 @@
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7450,12 +7450,12 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7467,13 +7467,13 @@
         </is>
       </c>
       <c r="G150" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H150" s="6" t="inlineStr"/>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -7486,22 +7486,22 @@
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>6051bd21daa83566</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>distrigomez seguros</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
@@ -7513,14 +7513,10 @@
         </is>
       </c>
       <c r="G151" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H151" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H151" s="6" t="inlineStr"/>
       <c r="I151" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7536,7 +7532,7 @@
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>1a7a81ed9e2a4160</t>
+          <t>6051bd21daa83566</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7546,12 +7542,12 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - campus neiva</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Universidad Cooperativa de Colombia</t>
+          <t>distrigomez seguros</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7563,10 +7559,14 @@
         </is>
       </c>
       <c r="G152" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H152" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7582,7 +7582,7 @@
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>a81375d5a4201305</t>
+          <t>1a7a81ed9e2a4160</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Digitador - bogotá</t>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>BUREAU VERITAS</t>
+          <t>Universidad Cooperativa de Colombia</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="G153" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H153" s="6" t="inlineStr"/>
@@ -7628,22 +7628,22 @@
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>9164fad20028594e</t>
+          <t>a81375d5a4201305</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Digitador(a) de nómina</t>
+          <t>Digitador - bogotá</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>BUREAU VERITAS</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="G154" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H154" s="6" t="inlineStr"/>
@@ -7674,7 +7674,7 @@
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>eb9248ba68f06027</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -7684,12 +7684,12 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="G155" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H155" s="6" t="inlineStr"/>
@@ -7720,22 +7720,22 @@
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ab0015399fb0fd5a</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Cali- asistente administrativo y contable</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>GERENCIA SELECTA SAS</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="G156" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H156" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>f151a5101fd2098d</t>
+          <t>ab0015399fb0fd5a</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo 212747-148845</t>
+          <t>Cali- asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>GERENCIA SELECTA SAS</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G157" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H157" s="6" t="inlineStr"/>
@@ -7812,7 +7812,7 @@
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2ad924abc5b01201</t>
+          <t>f151a5101fd2098d</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
+          <t>Auxiliar contable y administrativo 212747-148845</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="G158" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H158" s="6" t="inlineStr"/>
@@ -7858,7 +7858,7 @@
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>cb0d1367aba57052</t>
+          <t>2ad924abc5b01201</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="G159" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H159" s="6" t="inlineStr"/>
@@ -7904,7 +7904,7 @@
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>aa2ff4b012a2356b</t>
+          <t>cb0d1367aba57052</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Data entry specialist</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Naur Talent</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="G160" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H160" s="6" t="inlineStr"/>
@@ -7950,22 +7950,22 @@
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>0fb7813f6ca58c19</t>
+          <t>aa2ff4b012a2356b</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Assistant</t>
+          <t>Data entry specialist</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>NEO - New Estate Only</t>
+          <t>Naur Talent</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="G161" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H161" s="6" t="inlineStr"/>
@@ -7996,22 +7996,22 @@
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>e03aa4c6959d3eb4</t>
+          <t>0fb7813f6ca58c19</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Data Entry Assistant</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>NEO - New Estate Only</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8023,14 +8023,10 @@
         </is>
       </c>
       <c r="G162" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H162" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8046,7 +8042,7 @@
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>1a638820869677f4</t>
+          <t>e03aa4c6959d3eb4</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8056,12 +8052,12 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Valgroup Realty LLC</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
@@ -8073,7 +8069,7 @@
         </is>
       </c>
       <c r="G163" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H163" s="6" t="inlineStr">
@@ -8096,22 +8092,22 @@
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>d310964f2dc8e97e</t>
+          <t>1a638820869677f4</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:48</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz sena - auxiliar de servicio al cliente y ventas digitales remoto</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>M&amp;S VITAMINS SAS</t>
+          <t>Valgroup Realty LLC</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8123,10 +8119,14 @@
         </is>
       </c>
       <c r="G164" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aprendiz-sena-auxiliar-de-servicio-al-cliente-y-ventas-digitales-remoto-1886776017", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H164" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8142,7 +8142,7 @@
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>feadb7d6306993cf</t>
+          <t>d310964f2dc8e97e</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Aprendiz sena - auxiliar de servicio al cliente y ventas digitales remoto</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>M&amp;S VITAMINS SAS</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="G165" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886776241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aprendiz-sena-auxiliar-de-servicio-al-cliente-y-ventas-digitales-remoto-1886776017", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H165" s="6" t="inlineStr"/>
@@ -8188,22 +8188,22 @@
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>6dae76f41229d9ff</t>
+          <t>feadb7d6306993cf</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-10-05 19:48</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativo desde casa</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>POLITÉCNICO INTERNACIONAL DE OCCIDENTE</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8215,14 +8215,10 @@
         </is>
       </c>
       <c r="G166" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-desde-casa-personal-con-discapacidad-en-bogota-dc-5A794030AFDA0F8661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H166" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886776241", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H166" s="6" t="inlineStr"/>
       <c r="I166" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8238,7 +8234,7 @@
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>d59b1a44f5bebbdc</t>
+          <t>6dae76f41229d9ff</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -8248,12 +8244,12 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Auxiliar Administrativo desde casa</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>TALENT SPEAKERS COLOMBIA SAS</t>
+          <t>POLITÉCNICO INTERNACIONAL DE OCCIDENTE</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
@@ -8265,10 +8261,14 @@
         </is>
       </c>
       <c r="G167" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-1886775760", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H167" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-desde-casa-personal-con-discapacidad-en-bogota-dc-5A794030AFDA0F8661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I167" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8284,22 +8284,22 @@
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>594e79b4cd7df756</t>
+          <t>d59b1a44f5bebbdc</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:52</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo - contable y operativo</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>EFICACIA S.A.S</t>
+          <t>TALENT SPEAKERS COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="G168" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-contable-y-operativo-1886776165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-1886775760", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H168" s="6" t="inlineStr"/>
@@ -8330,7 +8330,7 @@
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>30c827aff6e8bff7</t>
+          <t>594e79b4cd7df756</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -8340,12 +8340,12 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Data Entry - Remote Work</t>
+          <t>Auxiliar administrativo - contable y operativo</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>INDI Staffing Services</t>
+          <t>EFICACIA S.A.S</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="G169" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-remote-work-at-indi-staffing-services-4476714759", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-contable-y-operativo-1886776165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H169" s="6" t="inlineStr"/>
@@ -8376,26 +8376,26 @@
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>30c827aff6e8bff7</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-07 17:52</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>INDI Staffing Services</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -8403,17 +8403,13 @@
         </is>
       </c>
       <c r="G170" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H170" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-remote-work-at-indi-staffing-services-4476714759", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H170" s="6" t="inlineStr"/>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -8426,26 +8422,26 @@
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>3b42a1ea5ac16f07</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Atención al cliente</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>CEO BUSSINES ADVICE SAS</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -8453,17 +8449,17 @@
         </is>
       </c>
       <c r="G171" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-atencion-al-cliente-en-bogota-dc-AC1B2F778774ED6561373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -8476,40 +8472,40 @@
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>838f39602895a4e7</t>
+          <t>478e11adcb76b027</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+          <t>Auxiliar administrativo almacen</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>AVSA S.A</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Hibrido</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="G172" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-almacen-1886777997", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H172" s="6" t="inlineStr"/>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -8522,26 +8518,26 @@
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>c2dea1f07ef53647</t>
+          <t>0df6c8526a27b503</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
+          <t>Auxiliar contable y administrativo - norte de bogotá</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -8549,13 +8545,13 @@
         </is>
       </c>
       <c r="G173" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-norte-de-bogota-1886766550", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H173" s="6" t="inlineStr"/>
       <c r="I173" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -8568,26 +8564,26 @@
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>d55c5bcc13a598dc</t>
+          <t>2e347f9b8c0b4b27</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:52</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Asesor(a) de servicio al cliente bilingüe</t>
+          <t>Digitador control de producción 634333</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Empresa en expansión</t>
+          <t>JOBANDTALENT CO SAS</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -8595,17 +8591,13 @@
         </is>
       </c>
       <c r="G174" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesora-de-servicio-al-cliente-bilingue-home-office-ingles-c1-con-experiencia-en-estados-unidos-D522AAAB4F954B8061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H174" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.500.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-control-de-produccion-634333-1886777795", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H174" s="6" t="inlineStr"/>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -8618,26 +8610,26 @@
     <row r="175" ht="22" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>1716d782af9a31c3</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Auxiliar i conciliaciones bancarias</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>PONTIFICIA UNIVERSID</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -8645,13 +8637,13 @@
         </is>
       </c>
       <c r="G175" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-i-conciliaciones-bancarias-1886774371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H175" s="6" t="inlineStr"/>
       <c r="I175" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -8664,26 +8656,26 @@
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>bcabe86161d0fafa</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Auxiliar administrativo contable</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Neuroactivo - Rodsal</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -8691,13 +8683,13 @@
         </is>
       </c>
       <c r="G176" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativo-contable-at-neuroactivo-rodsal-4476940406", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H176" s="6" t="inlineStr"/>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -8710,26 +8702,26 @@
     <row r="177" ht="22" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>c44dcea756fe7627</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -8737,21 +8729,401 @@
         </is>
       </c>
       <c r="G177" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4475962498", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H177" s="6" t="inlineStr"/>
       <c r="I177" s="3" t="inlineStr">
         <is>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr"/>
+    </row>
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>bab8c57875b70054</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>HOME BURGERS</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G178" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179" ht="22" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>e4553a32da3edf6d</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:07</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>SIIGO S.A.S</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G179" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I179" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180" ht="22" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>838f39602895a4e7</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:14</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>MANPOWER</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Hibrido</t>
+        </is>
+      </c>
+      <c r="G180" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H180" s="6" t="inlineStr"/>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181" ht="22" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>c2dea1f07ef53647</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:14</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>TALYCAP GLOBAL SAS</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G181" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H181" s="6" t="inlineStr"/>
+      <c r="I181" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>d55c5bcc13a598dc</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:52</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Asesor(a) de servicio al cliente bilingüe</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Empresa en expansión</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G182" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesora-de-servicio-al-cliente-bilingue-home-office-ingles-c1-con-experiencia-en-estados-unidos-D522AAAB4F954B8061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.500.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G183" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H183" s="6" t="inlineStr"/>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K177" s="3" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G184" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H184" s="6" t="inlineStr"/>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr"/>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G185" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H185" s="6" t="inlineStr"/>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K185"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8748,26 +8748,26 @@
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>c6719253a68b0b7b</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-09 17:30</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Asistente Virtual Bilingüe Remoto con Inglés Avanzado</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>Assistiq</t>
         </is>
       </c>
       <c r="E178" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -8775,17 +8775,17 @@
         </is>
       </c>
       <c r="G178" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-virtual-bilingue-remoto-con-ingles-avanzado-en-bogota-dc-648B6753680D9B9E61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H178" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -8798,7 +8798,7 @@
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>bab8c57875b70054</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>HOME BURGERS</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
@@ -8825,12 +8825,12 @@
         </is>
       </c>
       <c r="G179" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>$ 1.750.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -8848,22 +8848,22 @@
     <row r="180" ht="22" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>838f39602895a4e7</t>
+          <t>e4553a32da3edf6d</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>SIIGO S.A.S</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
@@ -8871,17 +8871,21 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Hibrido</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="G180" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H180" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -8894,22 +8898,22 @@
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>c2dea1f07ef53647</t>
+          <t>838f39602895a4e7</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
+          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
@@ -8917,17 +8921,17 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>Hibrido</t>
         </is>
       </c>
       <c r="G181" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H181" s="6" t="inlineStr"/>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -8940,22 +8944,22 @@
     <row r="182" ht="22" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>d55c5bcc13a598dc</t>
+          <t>c2dea1f07ef53647</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:52</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Asesor(a) de servicio al cliente bilingüe</t>
+          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Empresa en expansión</t>
+          <t>TALYCAP GLOBAL SAS</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -8967,14 +8971,10 @@
         </is>
       </c>
       <c r="G182" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesora-de-servicio-al-cliente-bilingue-home-office-ingles-c1-con-experiencia-en-estados-unidos-D522AAAB4F954B8061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.500.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H182" s="6" t="inlineStr"/>
       <c r="I182" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8990,26 +8990,26 @@
     <row r="183" ht="22" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>d55c5bcc13a598dc</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-10-07 17:52</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Asesor(a) de servicio al cliente bilingüe</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>Empresa en expansión</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -9017,13 +9017,17 @@
         </is>
       </c>
       <c r="G183" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H183" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesora-de-servicio-al-cliente-bilingue-home-office-ingles-c1-con-experiencia-en-estados-unidos-D522AAAB4F954B8061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -9036,22 +9040,22 @@
     <row r="184" ht="22" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>cd1036bcf66024dc</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Aprendiz practicante administrativo</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Bold.co</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -9063,7 +9067,7 @@
         </is>
       </c>
       <c r="G184" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H184" s="6" t="inlineStr"/>
@@ -9082,7 +9086,7 @@
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>dbdce1eb16060a6a</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -9092,12 +9096,12 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Auxiliar contable jr</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
@@ -9109,7 +9113,7 @@
         </is>
       </c>
       <c r="G185" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H185" s="6" t="inlineStr"/>
@@ -9124,6 +9128,52 @@
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr"/>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G186" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H186" s="6" t="inlineStr"/>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K186"/>
+  <dimension ref="A1:K188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3206,26 +3206,26 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>9b13ff35ed19b08e</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-10 16:18</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar logistico facturación</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3233,13 +3233,13 @@
         </is>
       </c>
       <c r="G59" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-logistico-facturacion-1886775031", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3262,16 +3262,16 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
@@ -3574,22 +3574,22 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3666,7 +3666,7 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr"/>
@@ -3712,22 +3712,22 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3758,22 +3758,22 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>62ab67e660127864</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y cartera</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>DON MAKINON</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
@@ -3804,22 +3804,22 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>39bf6fcb2b2ffb07</t>
+          <t>62ab67e660127864</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - medellín</t>
+          <t>Analista de facturación y cartera</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
+          <t>DON MAKINON</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
@@ -3850,22 +3850,22 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>65f969075798969c</t>
+          <t>39bf6fcb2b2ffb07</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación en salud</t>
+          <t>Analista de facturación - medellín</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-en-salud-1886772546", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
@@ -3896,26 +3896,26 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>65f969075798969c</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de facturación en salud</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-en-salud-1886772546", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3952,16 +3952,16 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -3969,13 +3969,13 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3998,16 +3998,16 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4015,17 +4015,13 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4038,7 +4034,7 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4048,12 +4044,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -4065,12 +4061,12 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4088,7 +4084,7 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4098,12 +4094,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4115,12 +4111,12 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4138,7 +4134,7 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4148,12 +4144,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
@@ -4165,7 +4161,7 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H79" s="6" t="inlineStr">
@@ -4188,7 +4184,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4198,12 +4194,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4215,7 +4211,7 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H80" s="6" t="inlineStr">
@@ -4238,7 +4234,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4248,12 +4244,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
@@ -4265,12 +4261,12 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4288,7 +4284,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4298,12 +4294,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4315,12 +4311,12 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4338,7 +4334,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4348,12 +4344,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4365,12 +4361,12 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.500.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4388,7 +4384,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4415,7 +4411,7 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -4438,7 +4434,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4465,7 +4461,7 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -4488,7 +4484,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4498,12 +4494,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4515,10 +4511,14 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H86" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4534,7 +4534,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -4580,7 +4580,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4590,12 +4590,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -4626,7 +4626,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H89" s="6" t="inlineStr"/>
@@ -4672,7 +4672,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H90" s="6" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4856,7 +4856,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4902,7 +4902,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5086,7 +5086,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5362,7 +5362,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5408,7 +5408,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5454,7 +5454,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5500,7 +5500,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5592,7 +5592,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5638,7 +5638,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
@@ -5776,7 +5776,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
@@ -5960,7 +5960,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
@@ -6052,7 +6052,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6144,7 +6144,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
@@ -6190,7 +6190,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H123" s="6" t="inlineStr"/>
@@ -6236,7 +6236,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
@@ -6328,7 +6328,7 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
@@ -6420,7 +6420,7 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
@@ -6466,7 +6466,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
@@ -6558,7 +6558,7 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
@@ -6604,7 +6604,7 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H132" s="6" t="inlineStr"/>
@@ -6650,7 +6650,7 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H133" s="6" t="inlineStr"/>
@@ -6696,7 +6696,7 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H134" s="6" t="inlineStr"/>
@@ -6742,7 +6742,7 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -6769,17 +6769,13 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H135" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -6792,22 +6788,22 @@
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -6819,17 +6815,17 @@
         </is>
       </c>
       <c r="G136" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
+          <t>OTE $25k - $35k</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -6842,7 +6838,7 @@
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6852,12 +6848,12 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
@@ -6869,10 +6865,14 @@
         </is>
       </c>
       <c r="G137" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H137" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6888,7 +6888,7 @@
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G138" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H138" s="6" t="inlineStr"/>
@@ -6934,7 +6934,7 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H139" s="6" t="inlineStr"/>
@@ -6980,7 +6980,7 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H140" s="6" t="inlineStr"/>
@@ -7026,7 +7026,7 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H141" s="6" t="inlineStr"/>
@@ -7072,7 +7072,7 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H142" s="6" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
@@ -7145,13 +7145,13 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="G144" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H144" s="6" t="inlineStr"/>
@@ -7210,7 +7210,7 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="G145" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H145" s="6" t="inlineStr"/>
@@ -7256,22 +7256,22 @@
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="G146" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="G147" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H147" s="6" t="inlineStr"/>
@@ -7348,7 +7348,7 @@
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7375,13 +7375,13 @@
         </is>
       </c>
       <c r="G148" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H148" s="6" t="inlineStr"/>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="G149" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H149" s="6" t="inlineStr"/>
@@ -7440,7 +7440,7 @@
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="G150" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H150" s="6" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
@@ -7513,13 +7513,13 @@
         </is>
       </c>
       <c r="G151" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H151" s="6" t="inlineStr"/>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -7532,22 +7532,22 @@
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>6051bd21daa83566</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>distrigomez seguros</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7559,14 +7559,10 @@
         </is>
       </c>
       <c r="G152" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H152" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H152" s="6" t="inlineStr"/>
       <c r="I152" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7582,7 +7578,7 @@
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>1a7a81ed9e2a4160</t>
+          <t>6051bd21daa83566</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -7592,12 +7588,12 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - campus neiva</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Universidad Cooperativa de Colombia</t>
+          <t>distrigomez seguros</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
@@ -7609,10 +7605,14 @@
         </is>
       </c>
       <c r="G153" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H153" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7628,7 +7628,7 @@
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>a81375d5a4201305</t>
+          <t>1a7a81ed9e2a4160</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Digitador - bogotá</t>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>BUREAU VERITAS</t>
+          <t>Universidad Cooperativa de Colombia</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="G154" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H154" s="6" t="inlineStr"/>
@@ -7674,22 +7674,22 @@
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>9164fad20028594e</t>
+          <t>a81375d5a4201305</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Digitador(a) de nómina</t>
+          <t>Digitador - bogotá</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>BUREAU VERITAS</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="G155" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H155" s="6" t="inlineStr"/>
@@ -7720,7 +7720,7 @@
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>eb9248ba68f06027</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="G156" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H156" s="6" t="inlineStr"/>
@@ -7766,22 +7766,22 @@
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>ab0015399fb0fd5a</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Cali- asistente administrativo y contable</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>GERENCIA SELECTA SAS</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G157" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H157" s="6" t="inlineStr"/>
@@ -7812,7 +7812,7 @@
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>f151a5101fd2098d</t>
+          <t>ab0015399fb0fd5a</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo 212747-148845</t>
+          <t>Cali- asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>GERENCIA SELECTA SAS</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="G158" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H158" s="6" t="inlineStr"/>
@@ -7858,7 +7858,7 @@
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>2ad924abc5b01201</t>
+          <t>f151a5101fd2098d</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
+          <t>Auxiliar contable y administrativo 212747-148845</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="G159" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H159" s="6" t="inlineStr"/>
@@ -7904,7 +7904,7 @@
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>cb0d1367aba57052</t>
+          <t>2ad924abc5b01201</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="G160" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H160" s="6" t="inlineStr"/>
@@ -7950,7 +7950,7 @@
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>aa2ff4b012a2356b</t>
+          <t>cb0d1367aba57052</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Data entry specialist</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Naur Talent</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="G161" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H161" s="6" t="inlineStr"/>
@@ -7996,22 +7996,22 @@
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>0fb7813f6ca58c19</t>
+          <t>aa2ff4b012a2356b</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Assistant</t>
+          <t>Data entry specialist</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>NEO - New Estate Only</t>
+          <t>Naur Talent</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="G162" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H162" s="6" t="inlineStr"/>
@@ -8042,22 +8042,22 @@
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>e03aa4c6959d3eb4</t>
+          <t>0fb7813f6ca58c19</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Data Entry Assistant</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>NEO - New Estate Only</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
@@ -8069,14 +8069,10 @@
         </is>
       </c>
       <c r="G163" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H163" s="6" t="inlineStr"/>
       <c r="I163" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8092,7 +8088,7 @@
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>1a638820869677f4</t>
+          <t>e03aa4c6959d3eb4</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -8102,12 +8098,12 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Valgroup Realty LLC</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8119,7 +8115,7 @@
         </is>
       </c>
       <c r="G164" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H164" s="6" t="inlineStr">
@@ -8142,22 +8138,22 @@
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>d310964f2dc8e97e</t>
+          <t>1a638820869677f4</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:48</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz sena - auxiliar de servicio al cliente y ventas digitales remoto</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>M&amp;S VITAMINS SAS</t>
+          <t>Valgroup Realty LLC</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
@@ -8169,10 +8165,14 @@
         </is>
       </c>
       <c r="G165" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aprendiz-sena-auxiliar-de-servicio-al-cliente-y-ventas-digitales-remoto-1886776017", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H165" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8188,7 +8188,7 @@
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>feadb7d6306993cf</t>
+          <t>d310964f2dc8e97e</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Aprendiz sena - auxiliar de servicio al cliente y ventas digitales remoto</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>M&amp;S VITAMINS SAS</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="G166" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886776241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aprendiz-sena-auxiliar-de-servicio-al-cliente-y-ventas-digitales-remoto-1886776017", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H166" s="6" t="inlineStr"/>
@@ -8234,22 +8234,22 @@
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>6dae76f41229d9ff</t>
+          <t>feadb7d6306993cf</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-10-05 19:48</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativo desde casa</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>POLITÉCNICO INTERNACIONAL DE OCCIDENTE</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
@@ -8261,14 +8261,10 @@
         </is>
       </c>
       <c r="G167" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-desde-casa-personal-con-discapacidad-en-bogota-dc-5A794030AFDA0F8661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H167" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886776241", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H167" s="6" t="inlineStr"/>
       <c r="I167" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8284,7 +8280,7 @@
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>d59b1a44f5bebbdc</t>
+          <t>6dae76f41229d9ff</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8294,12 +8290,12 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Auxiliar Administrativo desde casa</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>TALENT SPEAKERS COLOMBIA SAS</t>
+          <t>POLITÉCNICO INTERNACIONAL DE OCCIDENTE</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8311,10 +8307,14 @@
         </is>
       </c>
       <c r="G168" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-1886775760", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H168" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-desde-casa-personal-con-discapacidad-en-bogota-dc-5A794030AFDA0F8661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8330,22 +8330,22 @@
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>594e79b4cd7df756</t>
+          <t>d59b1a44f5bebbdc</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:52</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo - contable y operativo</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>EFICACIA S.A.S</t>
+          <t>TALENT SPEAKERS COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="G169" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-contable-y-operativo-1886776165", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-1886775760", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H169" s="6" t="inlineStr"/>
@@ -8376,7 +8376,7 @@
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>30c827aff6e8bff7</t>
+          <t>594e79b4cd7df756</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Data Entry - Remote Work</t>
+          <t>Auxiliar administrativo - contable y operativo</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>INDI Staffing Services</t>
+          <t>EFICACIA S.A.S</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="G170" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-remote-work-at-indi-staffing-services-4476714759", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-contable-y-operativo-1886776165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H170" s="6" t="inlineStr"/>
@@ -8422,22 +8422,22 @@
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>3b42a1ea5ac16f07</t>
+          <t>30c827aff6e8bff7</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:54</t>
+          <t>2026-10-07 17:52</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Atención al cliente</t>
+          <t>Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>CEO BUSSINES ADVICE SAS</t>
+          <t>INDI Staffing Services</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
@@ -8449,17 +8449,13 @@
         </is>
       </c>
       <c r="G171" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-atencion-al-cliente-en-bogota-dc-AC1B2F778774ED6561373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H171" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-remote-work-at-indi-staffing-services-4476714759", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H171" s="6" t="inlineStr"/>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -8472,7 +8468,7 @@
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>478e11adcb76b027</t>
+          <t>3b42a1ea5ac16f07</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8482,12 +8478,12 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo almacen</t>
+          <t>Atención al cliente</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>AVSA S.A</t>
+          <t>CEO BUSSINES ADVICE SAS</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
@@ -8499,13 +8495,17 @@
         </is>
       </c>
       <c r="G172" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-almacen-1886777997", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H172" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-atencion-al-cliente-en-bogota-dc-AC1B2F778774ED6561373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>0df6c8526a27b503</t>
+          <t>478e11adcb76b027</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo - norte de bogotá</t>
+          <t>Auxiliar administrativo almacen</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AVSA S.A</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G173" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-norte-de-bogota-1886766550", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-almacen-1886777997", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H173" s="6" t="inlineStr"/>
@@ -8564,7 +8564,7 @@
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>2e347f9b8c0b4b27</t>
+          <t>0df6c8526a27b503</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Digitador control de producción 634333</t>
+          <t>Auxiliar contable y administrativo - norte de bogotá</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>JOBANDTALENT CO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="G174" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-control-de-produccion-634333-1886777795", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-norte-de-bogota-1886766550", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H174" s="6" t="inlineStr"/>
@@ -8610,7 +8610,7 @@
     <row r="175" ht="22" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>1716d782af9a31c3</t>
+          <t>2e347f9b8c0b4b27</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -8620,12 +8620,12 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar i conciliaciones bancarias</t>
+          <t>Digitador control de producción 634333</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>PONTIFICIA UNIVERSID</t>
+          <t>JOBANDTALENT CO SAS</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="G175" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-i-conciliaciones-bancarias-1886774371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-control-de-produccion-634333-1886777795", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H175" s="6" t="inlineStr"/>
@@ -8656,7 +8656,7 @@
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>bcabe86161d0fafa</t>
+          <t>1716d782af9a31c3</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo contable</t>
+          <t>Auxiliar i conciliaciones bancarias</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Neuroactivo - Rodsal</t>
+          <t>PONTIFICIA UNIVERSID</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="G176" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativo-contable-at-neuroactivo-rodsal-4476940406", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-i-conciliaciones-bancarias-1886774371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H176" s="6" t="inlineStr"/>
@@ -8702,7 +8702,7 @@
     <row r="177" ht="22" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>c44dcea756fe7627</t>
+          <t>bcabe86161d0fafa</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Auxiliar administrativo contable</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Neuroactivo - Rodsal</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="G177" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4475962498", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativo-contable-at-neuroactivo-rodsal-4476940406", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H177" s="6" t="inlineStr"/>
@@ -8748,22 +8748,22 @@
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>c6719253a68b0b7b</t>
+          <t>c44dcea756fe7627</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 17:30</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Asistente Virtual Bilingüe Remoto con Inglés Avanzado</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Assistiq</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E178" s="7" t="n">
@@ -8775,14 +8775,10 @@
         </is>
       </c>
       <c r="G178" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-virtual-bilingue-remoto-con-ingles-avanzado-en-bogota-dc-648B6753680D9B9E61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H178" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4475962498", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H178" s="6" t="inlineStr"/>
       <c r="I178" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8798,26 +8794,26 @@
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>c6719253a68b0b7b</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-09 17:30</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Asistente Virtual Bilingüe Remoto con Inglés Avanzado</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>Assistiq</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -8825,17 +8821,17 @@
         </is>
       </c>
       <c r="G179" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-virtual-bilingue-remoto-con-ingles-avanzado-en-bogota-dc-648B6753680D9B9E61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -8848,26 +8844,26 @@
     <row r="180" ht="22" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>fed139d0477046bd</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-10 16:18</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Auxiliar administrativo bilingüe en barranquilla</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -8875,17 +8871,13 @@
         </is>
       </c>
       <c r="G180" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H180" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bilingue-en-barranquilla-1886773896", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H180" s="6" t="inlineStr"/>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -8898,22 +8890,22 @@
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>838f39602895a4e7</t>
+          <t>bab8c57875b70054</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>HOME BURGERS</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
@@ -8921,17 +8913,21 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Hibrido</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="G181" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H181" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -8944,22 +8940,22 @@
     <row r="182" ht="22" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>c2dea1f07ef53647</t>
+          <t>e4553a32da3edf6d</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>SIIGO S.A.S</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -8971,10 +8967,14 @@
         </is>
       </c>
       <c r="G182" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H182" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8990,22 +8990,22 @@
     <row r="183" ht="22" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>d55c5bcc13a598dc</t>
+          <t>838f39602895a4e7</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:52</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Asesor(a) de servicio al cliente bilingüe</t>
+          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Empresa en expansión</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
@@ -9013,21 +9013,17 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>Hibrido</t>
         </is>
       </c>
       <c r="G183" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesora-de-servicio-al-cliente-bilingue-home-office-ingles-c1-con-experiencia-en-estados-unidos-D522AAAB4F954B8061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H183" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.500.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H183" s="6" t="inlineStr"/>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -9040,26 +9036,26 @@
     <row r="184" ht="22" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>c2dea1f07ef53647</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>TALYCAP GLOBAL SAS</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -9067,13 +9063,13 @@
         </is>
       </c>
       <c r="G184" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H184" s="6" t="inlineStr"/>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -9086,26 +9082,26 @@
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>d55c5bcc13a598dc</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-10-07 17:52</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Asesor(a) de servicio al cliente bilingüe</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empresa en expansión</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -9113,13 +9109,17 @@
         </is>
       </c>
       <c r="G185" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H185" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesora-de-servicio-al-cliente-bilingue-home-office-ingles-c1-con-experiencia-en-estados-unidos-D522AAAB4F954B8061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I185" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -9132,22 +9132,22 @@
     <row r="186" ht="22" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>cd1036bcf66024dc</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Aprendiz practicante administrativo</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>Bold.co</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="G186" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H186" s="6" t="inlineStr"/>
@@ -9174,6 +9174,98 @@
         </is>
       </c>
       <c r="K186" s="3" t="inlineStr"/>
+    </row>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G187" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H187" s="6" t="inlineStr"/>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr"/>
+    </row>
+    <row r="188" ht="22" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G188" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H188" s="6" t="inlineStr"/>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K188"/>
+  <dimension ref="A1:K193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3252,26 +3252,26 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>d7b10cded83b71f2</t>
+          <t>05d5d5ace68df0c3</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-11 16:45</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Analista junior de facturación y telecomunicaciones</t>
+          <t>Auxiliar de facturacion hospitalaria</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>TP COLOMBIA</t>
+          <t>CLINICA SHAIO</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="G60" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalaria-1886627785", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3298,26 +3298,26 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>7c8e4b63802fbfdd</t>
+          <t>794c8af7f5852b96</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-11 16:45</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturacion - mocoa</t>
+          <t>Asistente de facturación y causación tipo ii - bogotá dc</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Clínica Medilaser S.A.S</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="n">
-        <v>0.68</v>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3325,13 +3325,13 @@
         </is>
       </c>
       <c r="G61" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-facturacion-y-causacion-tipo-ii-bogota-dc-1886770269", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3344,26 +3344,26 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>6a1a399dbe055821</t>
+          <t>a8d9caba91bc885f</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-11 16:45</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Auxiliar de facturación - consulta externa</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>CONTINAUTOS S.A.</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>0.68</v>
+          <t>HUSI</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3371,13 +3371,13 @@
         </is>
       </c>
       <c r="G62" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-consulta-externa-1886771488", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3390,26 +3390,26 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>8d104e6e0596782f</t>
+          <t>c4fd3a74127e4550</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-11 16:45</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - zipaquira</t>
+          <t>Aprendiz SENA – Gestión Documental</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="n">
-        <v>0.68</v>
+          <t>Inmov Global Network</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0.73</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3417,13 +3417,13 @@
         </is>
       </c>
       <c r="G63" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-sena-%E2%80%93-gesti%C3%B3n-documental-at-inmov-4477677360", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>30c981b787bd9e84</t>
+          <t>d7b10cded83b71f2</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3446,16 +3446,16 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación</t>
+          <t>Analista junior de facturación y telecomunicaciones</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>IMPULSO TEMPORAL SAS</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="n">
-        <v>0.68</v>
+          <t>TP COLOMBIA</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3463,13 +3463,13 @@
         </is>
       </c>
       <c r="G64" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-junior-de-facturacion-y-telecomunicaciones-1886758607", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 70/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>6ba85335e71be4cc</t>
+          <t>7c8e4b63802fbfdd</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturacion</t>
+          <t>Analista de facturacion - mocoa</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Experian Spanish Latam</t>
+          <t>Clínica Medilaser S.A.S</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="G65" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-mocoa-1886758704", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>0ba2c0ed565928ee</t>
+          <t>6a1a399dbe055821</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y gasto</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>AXA Partners</t>
+          <t>CONTINAUTOS S.A.</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="G66" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886758032", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2adbc58cb85c19c7</t>
+          <t>8d104e6e0596782f</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Analista de Facturación de servicios</t>
+          <t>Analista de facturación - zipaquira</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Américas BPS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="G67" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-zipaquira-1886769380", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
@@ -3620,12 +3620,12 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>a831855f10d17417</t>
+          <t>30c981b787bd9e84</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>IMPULSO TEMPORAL SAS</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="G68" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886751641", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -3666,22 +3666,22 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>d59df408fc52566d</t>
+          <t>6ba85335e71be4cc</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación- manejo de sap -</t>
+          <t>Analista de Facturacion</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Experian Spanish Latam</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G69" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturacion-at-experian-spanish-latam-4462035775", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H69" s="6" t="inlineStr"/>
@@ -3712,22 +3712,22 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>a1b8ba55f8922e99</t>
+          <t>0ba2c0ed565928ee</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Analista de cartera y facturación</t>
+          <t>Analista de facturación y gasto</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>AXA Partners</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="G70" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-y-gasto-at-axa-partners-4468296274", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H70" s="6" t="inlineStr"/>
@@ -3758,22 +3758,22 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>62e18b4bd9d42926</t>
+          <t>2adbc58cb85c19c7</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Analista de control operativo y facturación aduanera</t>
+          <t>Analista de Facturación de servicios</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>crane ww logistics</t>
+          <t>Américas BPS</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="G71" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/analista-de-facturaci%C3%B3n-de-servicios-at-am%C3%A9ricas-bps-4464891719", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
@@ -3804,22 +3804,22 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>62ab67e660127864</t>
+          <t>a831855f10d17417</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación y cartera</t>
+          <t>Analista de facturación</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>DON MAKINON</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="G72" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-1886756696", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
@@ -3850,22 +3850,22 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>39bf6fcb2b2ffb07</t>
+          <t>d59df408fc52566d</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación - medellín</t>
+          <t>Analista de facturación- manejo de sap -</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="G73" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-manejo-de-sap-1886756806", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H73" s="6" t="inlineStr"/>
@@ -3896,22 +3896,22 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>65f969075798969c</t>
+          <t>a1b8ba55f8922e99</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación en salud</t>
+          <t>Analista de cartera y facturación</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="G74" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-en-salud-1886772546", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-cartera-y-facturacion-1886741299", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H74" s="6" t="inlineStr"/>
@@ -3942,26 +3942,26 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>8ea64e48a843110e</t>
+          <t>62e18b4bd9d42926</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Digitación y Validación de Información</t>
+          <t>Analista de control operativo y facturación aduanera</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Hy Cite</t>
+          <t>crane ww logistics</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -3969,13 +3969,13 @@
         </is>
       </c>
       <c r="G75" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-control-operativo-y-facturacion-aduanera-1886771256", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -3988,26 +3988,26 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>0810fb157c23918e</t>
+          <t>62ab67e660127864</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Junior Tax Accountant / Data entry</t>
+          <t>Analista de facturación y cartera</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>George Dimov, CPA</t>
+          <t>DON MAKINON</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4015,13 +4015,13 @@
         </is>
       </c>
       <c r="G76" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-y-cartera-1886773105", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4034,26 +4034,26 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>b9e81da0bd12d416</t>
+          <t>39bf6fcb2b2ffb07</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Analista de facturación - medellín</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>VR RISK</t>
+          <t>SERVICIOS DE AUDITORIA Y CONSULTORIA DE NEGOCIOS SAS</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4061,17 +4061,13 @@
         </is>
       </c>
       <c r="G77" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-medellin-1886754458", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -4084,26 +4080,26 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>60a767236cb83e2b</t>
+          <t>65f969075798969c</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo y de Operaciones</t>
+          <t>Analista de facturación en salud</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Direct Home Solutions</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4111,17 +4107,13 @@
         </is>
       </c>
       <c r="G78" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.600.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-en-salud-1886772546", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H78" s="6" t="inlineStr"/>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -4134,26 +4126,26 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04855c966d018926</t>
+          <t>d9914a231367448b</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-11 16:45</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Analista de facturación en salud</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4161,17 +4153,13 @@
         </is>
       </c>
       <c r="G79" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-en-salud-1886772545", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 68/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -4184,7 +4172,7 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>a30e3afa7b66502b</t>
+          <t>8ea64e48a843110e</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4194,16 +4182,16 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>auxiliar administrativo/a</t>
+          <t>Auxiliar de Digitación y Validación de Información</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>ELITE SKIN ITALY S.A.S</t>
+          <t>Hy Cite</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4211,17 +4199,13 @@
         </is>
       </c>
       <c r="G80" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-de-digitaci%C3%B3n-y-validaci%C3%B3n-de-informaci%C3%B3n-at-hy-cite-4444163970", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H80" s="6" t="inlineStr"/>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 66/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4234,7 +4218,7 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>899512a1b5af847f</t>
+          <t>0810fb157c23918e</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4244,16 +4228,16 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>auxiliar contable y administrativo</t>
+          <t>Junior Tax Accountant / Data entry</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>AZ LOGICA SAS</t>
+          <t>George Dimov, CPA</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4261,17 +4245,13 @@
         </is>
       </c>
       <c r="G81" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>$ 2.000.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/junior-tax-accountant-data-entry-remote-at-george-dimov-cpa-4468922588", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H81" s="6" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 60/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -4284,7 +4264,7 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>0048b5632ef5acf6</t>
+          <t>b9e81da0bd12d416</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4294,12 +4274,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Asistente Administrativo</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Naonsoft</t>
+          <t>VR RISK</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4311,12 +4291,12 @@
         </is>
       </c>
       <c r="G82" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-remoto-en-bogota-dc-08C32BD16679929A61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -4334,7 +4314,7 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>062ee3244ed08bb4</t>
+          <t>60a767236cb83e2b</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4344,12 +4324,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Asistente de Servicio al Cliente y Administrativo</t>
+          <t>Asistente Administrativo y de Operaciones</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Health and Fitness</t>
+          <t>Direct Home Solutions</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
@@ -4361,12 +4341,12 @@
         </is>
       </c>
       <c r="G83" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-de-operaciones-remoto-en-pereira-737F61DE07AA2E7F61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>$ 2.500.000,00 (Mensual)</t>
+          <t>$ 2.600.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4384,7 +4364,7 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>90d5245bdef0186a</t>
+          <t>04855c966d018926</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4394,12 +4374,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4411,12 +4391,12 @@
         </is>
       </c>
       <c r="G84" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-F5B96991A8C617B661373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -4434,7 +4414,7 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>760f13e3724f6b31</t>
+          <t>a30e3afa7b66502b</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4444,12 +4424,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>auxiliar administrativo/a</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>ELITE SKIN ITALY S.A.S</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
@@ -4461,12 +4441,12 @@
         </is>
       </c>
       <c r="G85" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-virtual-remoto-con-o-sin-experiencia-en-bogota-dc-246C4633B2C1D28D61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -4484,7 +4464,7 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2d0d5c2d341e3d17</t>
+          <t>899512a1b5af847f</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4494,12 +4474,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y financiero</t>
+          <t>auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>SOLVO S.A.S</t>
+          <t>AZ LOGICA SAS</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -4511,12 +4491,12 @@
         </is>
       </c>
       <c r="G86" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-en-bogota-dc-E79FB52CC71B1AAF61373E686DCF3405", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>$ 2.000.000,00 (Mensual)</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -4534,7 +4514,7 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>63592c52663ab0e0</t>
+          <t>0048b5632ef5acf6</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4544,12 +4524,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo horario flexible remoto</t>
+          <t>Asistente Administrativo</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Empire Co</t>
+          <t>Naonsoft</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -4561,10 +4541,14 @@
         </is>
       </c>
       <c r="G87" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H87" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-en-medellin-268B37E50FB0D28461373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4580,7 +4564,7 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>729fb015086632d9</t>
+          <t>062ee3244ed08bb4</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4590,12 +4574,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
+          <t>Asistente de Servicio al Cliente y Administrativo</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Health and Fitness</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -4607,10 +4591,14 @@
         </is>
       </c>
       <c r="G88" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H88" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-de-servicio-al-cliente-y-administrativo-ingles-nativo-requerido-ingles-nativo-requerido-en-colombia-BA7538B8C571FA9F61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>$ 2.500.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4626,7 +4614,7 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>e4a3b83ad6ab6438</t>
+          <t>90d5245bdef0186a</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4636,12 +4624,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - licencia</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
@@ -4653,10 +4641,14 @@
         </is>
       </c>
       <c r="G89" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H89" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-bogota-dc-8B5C137D8309F1F661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4672,7 +4664,7 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2b1aa0caccddf7e4</t>
+          <t>760f13e3724f6b31</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4682,12 +4674,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -4699,10 +4691,14 @@
         </is>
       </c>
       <c r="G90" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H90" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-medellin-837774FFD1C514D261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4718,7 +4714,7 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>f864b0373b9419ab</t>
+          <t>2d0d5c2d341e3d17</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4728,12 +4724,12 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo -ciencias basicas</t>
+          <t>Asistente administrativo y financiero</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SOLVO S.A.S</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
@@ -4745,10 +4741,14 @@
         </is>
       </c>
       <c r="G91" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H91" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativo-y-financiero-b2-en-barranquilla-08F31F737CD14CED61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -4764,7 +4764,7 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>00a48d615f284d91</t>
+          <t>63592c52663ab0e0</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar administrativo horario flexible remoto</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Empire Co</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="G92" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-horario-flexible-remoto-1886769479", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H92" s="6" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>0544391db42d3941</t>
+          <t>729fb015086632d9</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Asistente de cuentas por pagar o tesoreria -remoto</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="G93" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-cuentas-por-pagar-o-tesoreria-remoto-1886744484", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
@@ -4856,7 +4856,7 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>e4338d6723631384</t>
+          <t>e4a3b83ad6ab6438</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y de logística corporativa</t>
+          <t>Auxiliar administrativo(a) - licencia</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="G94" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-licencia-1886759487", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
@@ -4902,7 +4902,7 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>54d4c3f98f954a41</t>
+          <t>2b1aa0caccddf7e4</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo educación continua</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Cruz Roja Colombiana Seccional Cundinamarca y Bogotá.</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="G95" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-1886753336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>e824af898bf9a932</t>
+          <t>f864b0373b9419ab</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo y financiero</t>
+          <t>Auxiliar administrativo -ciencias basicas</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G96" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-ciencias-basicas-1886759929", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>54c86d8a0d796617</t>
+          <t>00a48d615f284d91</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>ASISTALENTO SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="G97" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bienestar-universitario-1886744996", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>372b28276b98282f</t>
+          <t>0544391db42d3941</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Secretaria administrativa</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>FUNDACIÓN ANDES</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="G98" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886769676", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H98" s="6" t="inlineStr"/>
@@ -5086,7 +5086,7 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>cee8b3db11750755</t>
+          <t>e4338d6723631384</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo de obra</t>
+          <t>Auxiliar administrativo y de logística corporativa</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>GRUPO AR S.A.</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="G99" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-de-logistica-corporativa-1886765843", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H99" s="6" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>f86d411dd7ab31c0</t>
+          <t>54d4c3f98f954a41</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa supernumeraria</t>
+          <t>Auxiliar administrativo educación continua</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Grupo Good</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="G100" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-educacion-continua-1886750214", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H100" s="6" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02d246dd2c1d19fd</t>
+          <t>e824af898bf9a932</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva</t>
+          <t>Auxiliar administrativo y financiero</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="G101" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-y-financiero-1886753619", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H101" s="6" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>b56bb36e9fc82e1e</t>
+          <t>54c86d8a0d796617</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo/a</t>
+          <t>Auxiliar administrativa</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>ASISTALENTO SAS</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G102" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-1886767177", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>58fe156c45c49fc4</t>
+          <t>372b28276b98282f</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Asistente ejecutiva y personal de presidencia</t>
+          <t>Secretaria administrativa</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>FUNDACIÓN ANDES</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="G103" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/secretaria-administrativa-1886756322", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H103" s="6" t="inlineStr"/>
@@ -5316,7 +5316,7 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>c68c842aec0507f5</t>
+          <t>cee8b3db11750755</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y operativo</t>
+          <t>Auxiliar administrativo de obra</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>ALIANZA</t>
+          <t>GRUPO AR S.A.</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="G104" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-de-obra-1886747241", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
@@ -5362,7 +5362,7 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>e55c41f8f35d0d12</t>
+          <t>f86d411dd7ab31c0</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y comercial pereira</t>
+          <t>Asistente administrativa supernumeraria</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
+          <t>Grupo Good</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="G105" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-supernumeraria-1886762173", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -5408,7 +5408,7 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>0504d9833ad54912</t>
+          <t>02d246dd2c1d19fd</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo(a) at | bogotá</t>
+          <t>Asistente ejecutiva</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="G106" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-1886745926", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
@@ -5454,7 +5454,7 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>bacc38002882c624</t>
+          <t>b56bb36e9fc82e1e</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo</t>
+          <t>Asistente administrativo/a</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>POSSE HERRERA Y RUIZ</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="G107" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-a-1886747464", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H107" s="6" t="inlineStr"/>
@@ -5500,7 +5500,7 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>115c420d4e627838</t>
+          <t>58fe156c45c49fc4</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista y asistente administrativa</t>
+          <t>Asistente ejecutiva y personal de presidencia</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Colliers International Colombia S.A</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="G108" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-ejecutiva-y-personal-de-presidencia-1886765043", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H108" s="6" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>0eafe890d09dc027</t>
+          <t>c68c842aec0507f5</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
+          <t>Asistente administrativo y operativo</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>ALIANZA</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G109" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-operativo-1886769341", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H109" s="6" t="inlineStr"/>
@@ -5592,7 +5592,7 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>7fdb3ec2bb49ce90</t>
+          <t>e55c41f8f35d0d12</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa y contable</t>
+          <t>Asistente administrativa y comercial pereira</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
+          <t>EDITORIAL LA REPÚBLICA S.A.S.</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="G110" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-comercial-pereira-1886746894", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
@@ -5638,7 +5638,7 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>08014f384f124ec4</t>
+          <t>0504d9833ad54912</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativo(a) at | bogotá</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="G111" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativoa-at-bogota-1886765770", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H111" s="6" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>c62a542387886bca</t>
+          <t>bacc38002882c624</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable - villeta</t>
+          <t>Asistente administrativo</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>POSSE HERRERA Y RUIZ</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="G112" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-1886757128", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H112" s="6" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>fec983a79bc46288</t>
+          <t>115c420d4e627838</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativo y contable</t>
+          <t>Recepcionista y asistente administrativa</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>iLingo Integrated Solutions in Languages</t>
+          <t>Colliers International Colombia S.A</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G113" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-y-asistente-administrativa-1886769882", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H113" s="6" t="inlineStr"/>
@@ -5776,7 +5776,7 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>1871e0c68a13d38e</t>
+          <t>0eafe890d09dc027</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Asistente administrativa y contable - chía | ref. 1626544466-1</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="G114" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-chia-ref-16265444661-1886766808", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H114" s="6" t="inlineStr"/>
@@ -5822,7 +5822,7 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>6367348e3671a1aa</t>
+          <t>7fdb3ec2bb49ce90</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
+          <t>Asistente administrativa y contable</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ASESORES FINANCIEROS Y TRIBUTARIOS GR SAS</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G115" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-y-contable-1886758421", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>fa85204cef58799f</t>
+          <t>08014f384f124ec4</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="G116" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886759076", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H116" s="6" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>d8062d850cbf46a1</t>
+          <t>c62a542387886bca</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Digitador - 353703-113642</t>
+          <t>Asistente administrativo y contable - villeta</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="G117" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-villeta-1886758361", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
@@ -5960,7 +5960,7 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2f520ba083e2847f</t>
+          <t>fec983a79bc46288</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Digitador en planta de producción</t>
+          <t>Asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Prysmian Group - Procables</t>
+          <t>iLingo Integrated Solutions in Languages</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="G118" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativo-y-contable-1886747606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H118" s="6" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>475f3966c5302ff0</t>
+          <t>1871e0c68a13d38e</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="G119" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767163", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H119" s="6" t="inlineStr"/>
@@ -6052,7 +6052,7 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>107d0765b8dfce86</t>
+          <t>6367348e3671a1aa</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap, cartera y tesoreria</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="G120" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886760656", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H120" s="6" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>b1591783dbbcb1f9</t>
+          <t>fa85204cef58799f</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex</t>
+          <t>Asistente contable y administrativo con experiencia contable en sap - cartera y tesoreria</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="G121" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-administrativo-con-experiencia-contable-en-sap-cartera-y-tesoreria-1886766820", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H121" s="6" t="inlineStr"/>
@@ -6144,7 +6144,7 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>cfe8b8276b28373b</t>
+          <t>d8062d850cbf46a1</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Analista de aduana - digitador opencomex - santa marta</t>
+          <t>Digitador - 353703-113642</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="G122" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-353703113642-1886769566", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H122" s="6" t="inlineStr"/>
@@ -6190,7 +6190,7 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>01c7ac97b62a3626</t>
+          <t>2f520ba083e2847f</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar digitador(a) de contabilidad</t>
+          <t>Digitador en planta de producción</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Prysmian Group - Procables</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="G123" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-en-planta-de-produccion-1886722751", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H123" s="6" t="inlineStr"/>
@@ -6236,7 +6236,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2fc59d447ad455e1</t>
+          <t>475f3966c5302ff0</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Digitador comercial interno</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="G124" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886762323", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H124" s="6" t="inlineStr"/>
@@ -6282,7 +6282,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>e58059d4e095bd7a</t>
+          <t>107d0765b8dfce86</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Apoyo facturación - palmira</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>ALQUERIA</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="G125" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886770758", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H125" s="6" t="inlineStr"/>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>62e7c31c63a388da</t>
+          <t>b1591783dbbcb1f9</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Analista de aduana - digitador opencomex</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="G126" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-1886763468", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H126" s="6" t="inlineStr"/>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>6eafefaa9d4e76e6</t>
+          <t>cfe8b8276b28373b</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Analista de aduana - digitador opencomex - santa marta</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
@@ -6401,13 +6401,13 @@
         </is>
       </c>
       <c r="G127" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-aduana-digitador-opencomex-santa-marta-1886762869", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -6420,7 +6420,7 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>1ac2af8aa1b80d19</t>
+          <t>01c7ac97b62a3626</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista facturación en laboratorio clínico</t>
+          <t>Auxiliar digitador(a) de contabilidad</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="G128" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-digitadora-de-contabilidad-1886761791", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -6466,7 +6466,7 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>5fb21eaeba4e417d</t>
+          <t>2fc59d447ad455e1</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Gestor de Facturación e Ingresos // Remoto</t>
+          <t>Digitador comercial interno</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Siigo</t>
+          <t>TEMPORIZAR SERVICIOS TEMPORALES SAS</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="G129" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-comercial-interno-1886746080", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>acc279cbcc202e8c</t>
+          <t>e58059d4e095bd7a</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Clerk</t>
+          <t>Apoyo facturación - palmira</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Hired</t>
+          <t>ALQUERIA</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6539,13 +6539,13 @@
         </is>
       </c>
       <c r="G130" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/apoyo-facturacion-palmira-1886758686", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -6558,7 +6558,7 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>c9df64f69713d9c3</t>
+          <t>62e7c31c63a388da</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
@@ -6585,13 +6585,13 @@
         </is>
       </c>
       <c r="G131" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886761193", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>bfd4f2e4c8eb51d6</t>
+          <t>6eafefaa9d4e76e6</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist - Remote Work | REF#169097</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="G132" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886753959", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -6650,7 +6650,7 @@
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>f71b85e853980a5b</t>
+          <t>1ac2af8aa1b80d19</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Recepcionista facturación en laboratorio clínico</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
@@ -6677,13 +6677,13 @@
         </is>
       </c>
       <c r="G133" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-facturacion-en-laboratorio-clinico-1886746927", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -6696,7 +6696,7 @@
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>b124540f32e77f79</t>
+          <t>5fb21eaeba4e417d</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Digitador</t>
+          <t>Gestor de Facturación e Ingresos // Remoto</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Siigo</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6723,13 +6723,13 @@
         </is>
       </c>
       <c r="G134" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/gestor-de-facturaci%C3%B3n-e-ingresos-remoto-pcd-at-siigo-4463333674", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H134" s="6" t="inlineStr"/>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>648f264595161cd7</t>
+          <t>acc279cbcc202e8c</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Hired</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="G135" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-clerk-remote-at-hired-4466319108", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H135" s="6" t="inlineStr"/>
@@ -6788,7 +6788,7 @@
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>eb90ed56020b1176</t>
+          <t>c9df64f69713d9c3</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Inside Sales Contractor</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Credit Wellness, LLC</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -6815,17 +6815,13 @@
         </is>
       </c>
       <c r="G136" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>OTE $25k - $35k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4469179215", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -6838,22 +6834,22 @@
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ebabcd51596d0d3b</t>
+          <t>bfd4f2e4c8eb51d6</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Data Entry Specialist - Remote Work | REF#169097</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>ACTIVE ACCOUNTING GROUP</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
@@ -6865,14 +6861,10 @@
         </is>
       </c>
       <c r="G137" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-remote-work-ref%23169097-at-bairesdev-4140196697", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -6888,22 +6880,22 @@
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>e12bdf1aa280de03</t>
+          <t>f71b85e853980a5b</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -6915,7 +6907,7 @@
         </is>
       </c>
       <c r="G138" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-booth-4468950013", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H138" s="6" t="inlineStr"/>
@@ -6934,22 +6926,22 @@
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>b1fccbf6d15bddc2</t>
+          <t>b124540f32e77f79</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Digitador</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Dra Lina Bedoya Odontologia Estetica</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
@@ -6961,7 +6953,7 @@
         </is>
       </c>
       <c r="G139" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-at-iron-mountain-4468884742", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H139" s="6" t="inlineStr"/>
@@ -6980,22 +6972,22 @@
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>db6a52513ae159ab</t>
+          <t>648f264595161cd7</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar Administrativa de Vicepresidencia Bilingüe</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7007,7 +6999,7 @@
         </is>
       </c>
       <c r="G140" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativa-de-vicepresidencia-biling%C3%BCe-at-adecco-4469224990", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H140" s="6" t="inlineStr"/>
@@ -7026,22 +7018,22 @@
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>ae9358eb43bb2f5b</t>
+          <t>eb90ed56020b1176</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:56</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Inside Sales Contractor</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Credit Wellness, LLC</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
@@ -7053,13 +7045,17 @@
         </is>
       </c>
       <c r="G141" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H141" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/sales/inside-sales-contractor-2086540", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>OTE $25k - $35k</t>
+        </is>
+      </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -7072,7 +7068,7 @@
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>daa8b5315dfb38c2</t>
+          <t>ebabcd51596d0d3b</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7082,12 +7078,12 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - bogota</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>ACTIVE ACCOUNTING GROUP</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7099,10 +7095,14 @@
         </is>
       </c>
       <c r="G142" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H142" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-con-experiencia-en-el-santuario-C71D6812AE6D474061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7118,7 +7118,7 @@
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>2d35aa26ef7d8409</t>
+          <t>e12bdf1aa280de03</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Almacenista digitador</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="G143" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886768459", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H143" s="6" t="inlineStr"/>
@@ -7164,7 +7164,7 @@
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>a36cc8c2293d75bb</t>
+          <t>b1fccbf6d15bddc2</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Aux de facturacion - personas con discapacidad - bogota</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Quirón Prevención Colombia S.A.S</t>
+          <t>Dra Lina Bedoya Odontologia Estetica</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7191,13 +7191,13 @@
         </is>
       </c>
       <c r="G144" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886766293", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H144" s="6" t="inlineStr"/>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>e482852a389226cd</t>
+          <t>db6a52513ae159ab</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Ejecutivo de cuenta / facturación electrónica</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="G145" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767591", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>0dfab7dcd9959d45</t>
+          <t>ae9358eb43bb2f5b</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="G146" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -7302,22 +7302,22 @@
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>f89540ec077787b1</t>
+          <t>daa8b5315dfb38c2</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo</t>
+          <t>Auxiliar contable - sap - bogota</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>FUCS</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="G147" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-bogota-1886767164", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H147" s="6" t="inlineStr"/>
@@ -7348,12 +7348,12 @@
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>abffa88133eaa978</t>
+          <t>2d35aa26ef7d8409</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="G148" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886754273", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H148" s="6" t="inlineStr"/>
@@ -7394,12 +7394,12 @@
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>e4ad43c355211b6e</t>
+          <t>a36cc8c2293d75bb</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="G149" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886768842", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H149" s="6" t="inlineStr"/>
@@ -7440,22 +7440,22 @@
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>ebfb9e3d2b3f916c</t>
+          <t>e482852a389226cd</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clínico</t>
+          <t>Ejecutivo de cuenta / facturación electrónica</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="G150" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/ejecutivo-de-cuenta-facturacion-electronica-1886754585", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H150" s="6" t="inlineStr"/>
@@ -7486,17 +7486,17 @@
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>8478e893d783ed5e</t>
+          <t>0dfab7dcd9959d45</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-25 15:56</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Recepcion y facturacion de laboratorio clinico</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -7513,7 +7513,7 @@
         </is>
       </c>
       <c r="G151" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886771931", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H151" s="6" t="inlineStr"/>
@@ -7532,7 +7532,7 @@
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>d45621f8599206ec</t>
+          <t>f89540ec077787b1</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Specialist</t>
+          <t>Auxiliar administrativo</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>ZEISS Group</t>
+          <t>FUCS</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="G152" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-1886772558", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H152" s="6" t="inlineStr"/>
@@ -7578,22 +7578,22 @@
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>6051bd21daa83566</t>
+          <t>abffa88133eaa978</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Almacenista digitador</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>distrigomez seguros</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
@@ -7605,14 +7605,10 @@
         </is>
       </c>
       <c r="G153" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H153" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/almacenista-digitador-1886749637", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H153" s="6" t="inlineStr"/>
       <c r="I153" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7628,22 +7624,22 @@
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>1a7a81ed9e2a4160</t>
+          <t>e4ad43c355211b6e</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo(a) - campus neiva</t>
+          <t>Aux de facturacion - personas con discapacidad - bogota</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Universidad Cooperativa de Colombia</t>
+          <t>Quirón Prevención Colombia S.A.S</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7655,13 +7651,13 @@
         </is>
       </c>
       <c r="G154" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aux-de-facturacion-personas-con-discapacidad-bogota-1886772337", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H154" s="6" t="inlineStr"/>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -7674,22 +7670,22 @@
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>a81375d5a4201305</t>
+          <t>ebfb9e3d2b3f916c</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Digitador - bogotá</t>
+          <t>Recepcion y facturacion de laboratorio clínico</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>BUREAU VERITAS</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
@@ -7701,13 +7697,13 @@
         </is>
       </c>
       <c r="G155" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886767371", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -7720,22 +7716,22 @@
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>9164fad20028594e</t>
+          <t>8478e893d783ed5e</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Digitador(a) de nómina</t>
+          <t>Recepcion y facturacion de laboratorio clinico</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7747,13 +7743,13 @@
         </is>
       </c>
       <c r="G156" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcion-y-facturacion-de-laboratorio-clinico-1886760903", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H156" s="6" t="inlineStr"/>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -7766,22 +7762,22 @@
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>eb9248ba68f06027</t>
+          <t>d45621f8599206ec</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03</t>
+          <t>2026-09-26 15:05</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Data Entry Specialist</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>ZEISS Group</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
@@ -7793,7 +7789,7 @@
         </is>
       </c>
       <c r="G157" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-zeiss-group-4467880077", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H157" s="6" t="inlineStr"/>
@@ -7812,22 +7808,22 @@
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ab0015399fb0fd5a</t>
+          <t>6051bd21daa83566</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Cali- asistente administrativo y contable</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>GERENCIA SELECTA SAS</t>
+          <t>distrigomez seguros</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7839,10 +7835,14 @@
         </is>
       </c>
       <c r="G158" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H158" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-contable-y-administrativo-trabajo-desde-casa-en-pereira-3EEDFFC0D2447F8B61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -7858,22 +7858,22 @@
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>f151a5101fd2098d</t>
+          <t>1a7a81ed9e2a4160</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo 212747-148845</t>
+          <t>Auxiliar administrativo(a) - campus neiva</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Universidad Cooperativa de Colombia</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="G159" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativoa-campus-neiva-1886773020", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H159" s="6" t="inlineStr"/>
@@ -7904,22 +7904,22 @@
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>2ad924abc5b01201</t>
+          <t>a81375d5a4201305</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-28 18:38</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
+          <t>Digitador - bogotá</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>BUREAU VERITAS</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="G160" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-bogota-1886762709", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H160" s="6" t="inlineStr"/>
@@ -7950,22 +7950,22 @@
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>cb0d1367aba57052</t>
+          <t>9164fad20028594e</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Client Intake and Data Entry Specialist</t>
+          <t>Digitador(a) de nómina</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Job Duck</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="G161" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitadora-de-nomina-1886773344", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H161" s="6" t="inlineStr"/>
@@ -7996,22 +7996,22 @@
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>aa2ff4b012a2356b</t>
+          <t>eb9248ba68f06027</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:51</t>
+          <t>2026-09-29 17:03</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Data entry specialist</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Naur Talent</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="G162" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4471917951", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H162" s="6" t="inlineStr"/>
@@ -8042,22 +8042,22 @@
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>0fb7813f6ca58c19</t>
+          <t>ab0015399fb0fd5a</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Data Entry Assistant</t>
+          <t>Cali- asistente administrativo y contable</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>NEO - New Estate Only</t>
+          <t>GERENCIA SELECTA SAS</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="G163" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/cali-asistente-administrativo-y-contable-1886774199", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H163" s="6" t="inlineStr"/>
@@ -8088,22 +8088,22 @@
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>e03aa4c6959d3eb4</t>
+          <t>f151a5101fd2098d</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
+          <t>Auxiliar contable y administrativo 212747-148845</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8115,14 +8115,10 @@
         </is>
       </c>
       <c r="G164" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-212747148845-1886774053", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H164" s="6" t="inlineStr"/>
       <c r="I164" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8138,22 +8134,22 @@
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>1a638820869677f4</t>
+          <t>2ad924abc5b01201</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Auxiliar administrativa y contable- mosquera- 1626546205-1</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Valgroup Realty LLC</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
@@ -8165,14 +8161,10 @@
         </is>
       </c>
       <c r="G165" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H165" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativa-y-contable-mosquera-16265462051-1886773852", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H165" s="6" t="inlineStr"/>
       <c r="I165" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8188,22 +8180,22 @@
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>d310964f2dc8e97e</t>
+          <t>cb0d1367aba57052</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:48</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz sena - auxiliar de servicio al cliente y ventas digitales remoto</t>
+          <t>Client Intake and Data Entry Specialist</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>M&amp;S VITAMINS SAS</t>
+          <t>Job Duck</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8215,7 +8207,7 @@
         </is>
       </c>
       <c r="G166" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aprendiz-sena-auxiliar-de-servicio-al-cliente-y-ventas-digitales-remoto-1886776017", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/client-intake-and-data-entry-specialist-at-job-duck-4473785617", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H166" s="6" t="inlineStr"/>
@@ -8234,22 +8226,22 @@
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>feadb7d6306993cf</t>
+          <t>aa2ff4b012a2356b</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:48</t>
+          <t>2026-09-30 16:51</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Asistente administrativa</t>
+          <t>Data entry specialist</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>MENTORHUB COLOMBIA</t>
+          <t>Naur Talent</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
@@ -8261,7 +8253,7 @@
         </is>
       </c>
       <c r="G167" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886776241", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-specialist-at-naur-talent-4473907227", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H167" s="6" t="inlineStr"/>
@@ -8280,22 +8272,22 @@
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>6dae76f41229d9ff</t>
+          <t>0fb7813f6ca58c19</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-10-01 17:28</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Administrativo desde casa</t>
+          <t>Data Entry Assistant</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>POLITÉCNICO INTERNACIONAL DE OCCIDENTE</t>
+          <t>NEO - New Estate Only</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8307,14 +8299,10 @@
         </is>
       </c>
       <c r="G168" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-desde-casa-personal-con-discapacidad-en-bogota-dc-5A794030AFDA0F8661373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H168" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-assistant-at-neo-new-estate-only-4474342064", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H168" s="6" t="inlineStr"/>
       <c r="I168" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8330,22 +8318,22 @@
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>d59b1a44f5bebbdc</t>
+          <t>e03aa4c6959d3eb4</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo</t>
+          <t>Auxiliar administrativo/a Vacante Inclusiva para personas con Discapacidad</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>TALENT SPEAKERS COLOMBIA SAS</t>
+          <t>CENTRO DE EMPLEO Y TALENTO COLSUBSIDIO</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
@@ -8357,10 +8345,14 @@
         </is>
       </c>
       <c r="G169" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-1886775760", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H169" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativoa-vacante-inclusiva-para-personas-con-discapacidad-en-bogota-dc-C48470AF94C2CBCC61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8376,22 +8368,22 @@
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>594e79b4cd7df756</t>
+          <t>1a638820869677f4</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:52</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo - contable y operativo</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>EFICACIA S.A.S</t>
+          <t>Valgroup Realty LLC</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8403,10 +8395,14 @@
         </is>
       </c>
       <c r="G170" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-contable-y-operativo-1886776165", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H170" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-administrativa-con-conocimiento-del-idioma-ingles-en-bucaramanga-E109D498CC2B20FD61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8422,22 +8418,22 @@
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>30c827aff6e8bff7</t>
+          <t>d310964f2dc8e97e</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:52</t>
+          <t>2026-10-05 19:48</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Data Entry - Remote Work</t>
+          <t>Aprendiz sena - auxiliar de servicio al cliente y ventas digitales remoto</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>INDI Staffing Services</t>
+          <t>M&amp;S VITAMINS SAS</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
@@ -8449,7 +8445,7 @@
         </is>
       </c>
       <c r="G171" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-remote-work-at-indi-staffing-services-4476714759", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/aprendiz-sena-auxiliar-de-servicio-al-cliente-y-ventas-digitales-remoto-1886776017", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H171" s="6" t="inlineStr"/>
@@ -8468,22 +8464,22 @@
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>3b42a1ea5ac16f07</t>
+          <t>feadb7d6306993cf</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:54</t>
+          <t>2026-10-05 19:48</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Atención al cliente</t>
+          <t>Asistente administrativa</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>CEO BUSSINES ADVICE SAS</t>
+          <t>MENTORHUB COLOMBIA</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
@@ -8495,17 +8491,13 @@
         </is>
       </c>
       <c r="G172" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-atencion-al-cliente-en-bogota-dc-AC1B2F778774ED6561373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H172" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-administrativa-1886776241", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H172" s="6" t="inlineStr"/>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -8518,22 +8510,22 @@
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>478e11adcb76b027</t>
+          <t>6dae76f41229d9ff</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:54</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo almacen</t>
+          <t>Auxiliar Administrativo desde casa</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>AVSA S.A</t>
+          <t>POLITÉCNICO INTERNACIONAL DE OCCIDENTE</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
@@ -8545,10 +8537,14 @@
         </is>
       </c>
       <c r="G173" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-almacen-1886777997", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H173" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-administrativo-desde-casa-personal-con-discapacidad-en-bogota-dc-5A794030AFDA0F8661373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I173" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8564,22 +8560,22 @@
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>0df6c8526a27b503</t>
+          <t>d59b1a44f5bebbdc</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:54</t>
+          <t>2026-10-06 17:14</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable y administrativo - norte de bogotá</t>
+          <t>Auxiliar contable y administrativo</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>TALENT SPEAKERS COLOMBIA SAS</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
@@ -8591,7 +8587,7 @@
         </is>
       </c>
       <c r="G174" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-norte-de-bogota-1886766550", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-1886775760", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H174" s="6" t="inlineStr"/>
@@ -8610,22 +8606,22 @@
     <row r="175" ht="22" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>2e347f9b8c0b4b27</t>
+          <t>594e79b4cd7df756</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:54</t>
+          <t>2026-10-07 17:52</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Digitador control de producción 634333</t>
+          <t>Auxiliar administrativo - contable y operativo</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>JOBANDTALENT CO SAS</t>
+          <t>EFICACIA S.A.S</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
@@ -8637,7 +8633,7 @@
         </is>
       </c>
       <c r="G175" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-control-de-produccion-634333-1886777795", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-contable-y-operativo-1886776165", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H175" s="6" t="inlineStr"/>
@@ -8656,22 +8652,22 @@
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>1716d782af9a31c3</t>
+          <t>30c827aff6e8bff7</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:54</t>
+          <t>2026-10-07 17:52</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar i conciliaciones bancarias</t>
+          <t>Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>PONTIFICIA UNIVERSID</t>
+          <t>INDI Staffing Services</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
@@ -8683,7 +8679,7 @@
         </is>
       </c>
       <c r="G176" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-i-conciliaciones-bancarias-1886774371", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/data-entry-remote-work-at-indi-staffing-services-4476714759", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H176" s="6" t="inlineStr"/>
@@ -8702,7 +8698,7 @@
     <row r="177" ht="22" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>bcabe86161d0fafa</t>
+          <t>3b42a1ea5ac16f07</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -8712,12 +8708,12 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo contable</t>
+          <t>Atención al cliente</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Neuroactivo - Rodsal</t>
+          <t>CEO BUSSINES ADVICE SAS</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
@@ -8729,13 +8725,17 @@
         </is>
       </c>
       <c r="G177" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativo-contable-at-neuroactivo-rodsal-4476940406", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H177" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-atencion-al-cliente-en-bogota-dc-AC1B2F778774ED6561373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I177" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Alta coincidencia técnica en Gestión Administrativa, Documental y Archivo. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -8748,7 +8748,7 @@
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>c44dcea756fe7627</t>
+          <t>478e11adcb76b027</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Young Professional – Data Entry - Remote Work</t>
+          <t>Auxiliar administrativo almacen</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>AVSA S.A</t>
         </is>
       </c>
       <c r="E178" s="7" t="n">
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="G178" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4475962498", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-almacen-1886777997", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H178" s="6" t="inlineStr"/>
@@ -8794,22 +8794,22 @@
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>c6719253a68b0b7b</t>
+          <t>0df6c8526a27b503</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 17:30</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Asistente Virtual Bilingüe Remoto con Inglés Avanzado</t>
+          <t>Auxiliar contable y administrativo - norte de bogotá</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Assistiq</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
@@ -8821,14 +8821,10 @@
         </is>
       </c>
       <c r="G179" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-virtual-bilingue-remoto-con-ingles-avanzado-en-bogota-dc-648B6753680D9B9E61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H179" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-y-administrativo-norte-de-bogota-1886766550", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H179" s="6" t="inlineStr"/>
       <c r="I179" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -8844,22 +8840,22 @@
     <row r="180" ht="22" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>fed139d0477046bd</t>
+          <t>2e347f9b8c0b4b27</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:18</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar administrativo bilingüe en barranquilla</t>
+          <t>Digitador control de producción 634333</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>JOBANDTALENT CO SAS</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
@@ -8871,7 +8867,7 @@
         </is>
       </c>
       <c r="G180" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bilingue-en-barranquilla-1886773896", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/digitador-control-de-produccion-634333-1886777795", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H180" s="6" t="inlineStr"/>
@@ -8890,26 +8886,26 @@
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>bab8c57875b70054</t>
+          <t>1716d782af9a31c3</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
+          <t>Auxiliar i conciliaciones bancarias</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>HOME BURGERS</t>
+          <t>PONTIFICIA UNIVERSID</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
@@ -8917,17 +8913,13 @@
         </is>
       </c>
       <c r="G181" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H181" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-i-conciliaciones-bancarias-1886774371", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H181" s="6" t="inlineStr"/>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -8940,26 +8932,26 @@
     <row r="182" ht="22" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>e4553a32da3edf6d</t>
+          <t>bcabe86161d0fafa</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Asesor de Servicio al Cliente / Remoto</t>
+          <t>Auxiliar administrativo contable</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>SIIGO S.A.S</t>
+          <t>Neuroactivo - Rodsal</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
@@ -8967,17 +8959,13 @@
         </is>
       </c>
       <c r="G182" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>$ 1.750.905,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-administrativo-contable-at-neuroactivo-rodsal-4476940406", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H182" s="6" t="inlineStr"/>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -8990,40 +8978,40 @@
     <row r="183" ht="22" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>838f39602895a4e7</t>
+          <t>c44dcea756fe7627</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-10-08 17:54</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
+          <t>Young Professional – Data Entry - Remote Work</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>MANPOWER</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Hibrido</t>
+          <t>Remoto</t>
         </is>
       </c>
       <c r="G183" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/young-professional-%E2%80%93-data-entry-remote-work-at-bairesdev-4475962498", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H183" s="6" t="inlineStr"/>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -9036,26 +9024,26 @@
     <row r="184" ht="22" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>c2dea1f07ef53647</t>
+          <t>c6719253a68b0b7b</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:14</t>
+          <t>2026-10-09 17:30</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
+          <t>Asistente Virtual Bilingüe Remoto con Inglés Avanzado</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>TALYCAP GLOBAL SAS</t>
+          <t>Assistiq</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -9063,13 +9051,17 @@
         </is>
       </c>
       <c r="G184" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H184" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asistente-virtual-bilingue-remoto-con-ingles-avanzado-en-bogota-dc-648B6753680D9B9E61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -9082,26 +9074,26 @@
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>d55c5bcc13a598dc</t>
+          <t>fed139d0477046bd</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:52</t>
+          <t>2026-10-10 16:18</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Asesor(a) de servicio al cliente bilingüe</t>
+          <t>Auxiliar administrativo bilingüe en barranquilla</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Empresa en expansión</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -9109,17 +9101,13 @@
         </is>
       </c>
       <c r="G185" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesora-de-servicio-al-cliente-bilingue-home-office-ingles-c1-con-experiencia-en-estados-unidos-D522AAAB4F954B8061373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>$ 3.500.000,00 (Mensual)</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-bilingue-en-barranquilla-1886773896", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H185" s="6" t="inlineStr"/>
       <c r="I185" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 58/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -9132,26 +9120,26 @@
     <row r="186" ht="22" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>cd1036bcf66024dc</t>
+          <t>bab8c57875b70054</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 15:05</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Aprendiz practicante administrativo</t>
+          <t>Analista de Servicio al Cliente Digital / Personal con Discapacidad</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Bold.co</t>
+          <t>HOME BURGERS</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -9159,13 +9147,17 @@
         </is>
       </c>
       <c r="G186" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H186" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-analista-de-servicio-al-cliente-digital-personal-con-discapacidad-en-bogota-dc-11CE94961396D4CF61373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.000,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -9178,26 +9170,26 @@
     <row r="187" ht="22" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>dbdce1eb16060a6a</t>
+          <t>e4553a32da3edf6d</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable jr</t>
+          <t>Asesor de Servicio al Cliente / Remoto</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>SIIGO S.A.S</t>
         </is>
       </c>
       <c r="E187" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -9205,13 +9197,17 @@
         </is>
       </c>
       <c r="G187" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H187" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesor-de-servicio-al-cliente-remoto-en-bogota-dc-00C206C9966382F961373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>$ 1.750.905,00 (Mensual)</t>
+        </is>
+      </c>
       <c r="I187" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -9224,48 +9220,282 @@
     <row r="188" ht="22" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>550ad8afea6faf9b</t>
+          <t>838f39602895a4e7</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:38</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar Contable Junior</t>
+          <t>Analista de facturación (billing analyst)/ inglés b2 /híbrido</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Ariadna Communications Group</t>
+          <t>MANPOWER</t>
         </is>
       </c>
       <c r="E188" s="7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Remoto</t>
+          <t>Hibrido</t>
         </is>
       </c>
       <c r="G188" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/analista-de-facturacion-billing-analyst-ingles-b2-hibrido-1886773841", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H188" s="6" t="inlineStr"/>
       <c r="I188" s="3" t="inlineStr">
         <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: Modalidad híbrida / parcial. Alerta: Modalidad híbrida puede requerir presencia ocasional.</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr"/>
+    </row>
+    <row r="189" ht="22" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>c2dea1f07ef53647</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:14</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Consultor sap fi-gl / fi-aa s/4hana - remoto colombia</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>TALYCAP GLOBAL SAS</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G189" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/consultor-sap-figl-fiaa-s-4hana-remoto-colombia-1886776900", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H189" s="6" t="inlineStr"/>
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr"/>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>d55c5bcc13a598dc</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:52</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Asesor(a) de servicio al cliente bilingüe</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Empresa en expansión</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G190" s="5">
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-asesora-de-servicio-al-cliente-bilingue-home-office-ingles-c1-con-experiencia-en-estados-unidos-D522AAAB4F954B8061373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>$ 3.500.000,00 (Mensual)</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 53/100 - Afinidad Moderada] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr"/>
+    </row>
+    <row r="191" ht="22" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>cd1036bcf66024dc</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:05</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Aprendiz practicante administrativo</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Bold.co</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G191" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/aprendiz-practicante-administrativo-etapa-productiva-at-bold-4457032181", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H191" s="6" t="inlineStr"/>
+      <c r="I191" s="3" t="inlineStr">
+        <is>
           <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t>Nueva</t>
-        </is>
-      </c>
-      <c r="K188" s="3" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr"/>
+    </row>
+    <row r="192" ht="22" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>dbdce1eb16060a6a</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar contable jr</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G192" s="5">
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-jr-1886767584", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H192" s="6" t="inlineStr"/>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr"/>
+    </row>
+    <row r="193" ht="22" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>550ad8afea6faf9b</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:38</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable Junior</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Ariadna Communications Group</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="G193" s="5">
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/auxiliar-contable-junior-at-ariadna-communications-group-4472764062", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H193" s="6" t="inlineStr"/>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>[Afinidad: 50/100 - Afinidad Moderada] Afinidad en rol base (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>Nueva</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/output/profile_6_auxiliar_administrativo_tracker.xlsx
+++ b/output/profile_6_auxiliar_administrativo_tracker.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K193"/>
+  <dimension ref="A1:K198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -618,26 +618,26 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>e525f145f275012a</t>
+          <t>3d6eefdfe8f8b83b</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-12 20:20</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Remote Office Assistant</t>
+          <t>Auxiliar administrativo/ facturación hospitalario</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Coalition Technologies</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.78</v>
+        <v>0.93</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -645,17 +645,13 @@
         </is>
       </c>
       <c r="G3" s="5">
-        <f>HYPERLINK("https://remotive.com/remote-jobs/marketing/remote-office-assistant-1680495", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>$35,3k- $52k</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-administrativo-facturacion-hospitalario-1886767814", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 78/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 93/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -668,22 +664,22 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3c78d827079503ad</t>
+          <t>e525f145f275012a</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14</t>
+          <t>2026-09-24 16:07</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Digitador SAP</t>
+          <t>Remote Office Assistant</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Industrias Puropollo S.A.S</t>
+          <t>Coalition Technologies</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -695,13 +691,17 @@
         </is>
       </c>
       <c r="G4" s="5">
-        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-sap-at-industrias-puropollo-s-a-s-4475052500", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H4" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://remotive.com/remote-jobs/marketing/remote-office-assistant-1680495", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>$35,3k- $52k</t>
+        </is>
+      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 78/100 - Alta Afinidad] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 78/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -714,26 +714,26 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>5e69bdc3d8d68672</t>
+          <t>3c78d827079503ad</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:07</t>
+          <t>2026-10-03 15:14</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de Facturación Teletrabajo</t>
+          <t>Digitador SAP</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Importante empresa del sector</t>
+          <t>Industrias Puropollo S.A.S</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -741,17 +741,13 @@
         </is>
       </c>
       <c r="G5" s="5">
-        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-de-facturacion-teletrabajo-en-cali-436F39785C023D1261373E686DCF3405", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Remoto</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://co.linkedin.com/jobs/view/digitador-sap-at-industrias-puropollo-s-a-s-4475052500", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
+          <t>[Afinidad: 78/100 - Alta Afinidad] Afinidad moderada en áreas técnicas del cargo (Auxiliar Administrativo / Asistente Virtual). Modalidad: 100% Remoto en Colombia confirmado.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -764,7 +760,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>7cf82a12d60b65c7</t>
+          <t>5e69bdc3d8d68672</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -774,12 +770,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable- conocimiento y dominio en erp siigo nube</t>
+          <t>Auxiliar de Facturación Teletrabajo</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Importante empresa del sector</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -791,10 +787,14 @@
         </is>
       </c>
       <c r="G6" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-conocimiento-y-dominio-en-erp-siigo-nube-1886749387", "Ver Vacante")</f>
-        <v/>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
+        <f>HYPERLINK("https://co.computrabajo.com/ofertas-de-trabajo/oferta-de-trabajo-de-auxiliar-de-facturacion-teletrabajo-en-cali-436F39785C023D1261373E686DCF3405", "Ver Vacante")</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t>[Afinidad: 73/100 - Alta Afinidad] Alta coincidencia técnica en Herramientas Ofimáticas, Excel y Soporte Contable / Facturación. Modalidad: 100% Remoto en Colombia confirmado.</t>
@@ -810,7 +810,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>80dcaff6c76c4739</t>
+          <t>7cf82a12d60b65c7</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Auxiliar contable- conocimiento y dominio en erp siigo nube</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Tower Consulting WorldWide SAS</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G7" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886756116", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-conocimiento-y-dominio-en-erp-siigo-nube-1886749387", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
@@ -856,7 +856,7 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2a5b492f2cf08a86</t>
+          <t>80dcaff6c76c4739</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion // yopal medio tiempo</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Tower Consulting WorldWide SAS</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="G8" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-yopal-medio-tiempo-1886767206", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886756116", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="inlineStr"/>
@@ -902,7 +902,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>4e81a6e21cf2499c</t>
+          <t>2a5b492f2cf08a86</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar contable - sap - facturacion electronica - bogota</t>
+          <t>Auxiliar de facturacion // yopal medio tiempo</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>ADECCO COLOMBIA S A</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="G9" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-facturacion-electronica-bogota-1886767171", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-yopal-medio-tiempo-1886767206", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="inlineStr"/>
@@ -948,7 +948,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>5b72a870b18cd8dd</t>
+          <t>4e81a6e21cf2499c</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Auxiliar contable - sap - facturacion electronica - bogota</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ADECCO COLOMBIA S A</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="G10" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886767351", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-contable-sap-facturacion-electronica-bogota-1886767171", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="inlineStr"/>
@@ -994,7 +994,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>aaf3a1241a43d56a</t>
+          <t>5b72a870b18cd8dd</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Asistente de facturación y despachos - yumbo</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>DISAN COLOMBIA S.A.S</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="G11" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-facturacion-y-despachos-yumbo-1886765290", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886767351", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
@@ -1040,7 +1040,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>4c6e2ae68998ff1f</t>
+          <t>aaf3a1241a43d56a</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Asistente de facturación y despachos - yumbo</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>DISAN COLOMBIA S.A.S</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="G12" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-ibague-1886770122", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-facturacion-y-despachos-yumbo-1886765290", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H12" s="6" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>dad6a39f05eb0872</t>
+          <t>4c6e2ae68998ff1f</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación hospitalario</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>INSTITUTO ROOSEVELT</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="G13" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalario-1886760993", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-ibague-1886770122", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>c80879dace821f2d</t>
+          <t>dad6a39f05eb0872</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación - 1626343701-25</t>
+          <t>Auxiliar de facturación hospitalario</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>INSTITUTO ROOSEVELT</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="G14" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-162634370125-1886768889", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalario-1886760993", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>a581954268b43f5e</t>
+          <t>c80879dace821f2d</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion hospitalaria</t>
+          <t>Auxiliar de facturación - 1626343701-25</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="G15" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalaria-1886760847", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-162634370125-1886768889", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>f19945acad64eb39</t>
+          <t>a581954268b43f5e</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>CLINICA SHAIO</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="G16" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalaria-1886377445", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalaria-1886760847", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>c5b127601236be94</t>
+          <t>f19945acad64eb39</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion // sector salud laboratorio clinico /// villavicencio meta</t>
+          <t>Auxiliar de facturacion hospitalaria</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>CLINICA SHAIO</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="G17" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-sector-salud-laboratorio-clinico-villavicencio-meta-1886746288", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-hospitalaria-1886377445", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H17" s="6" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>6bf2402aaa779ade</t>
+          <t>c5b127601236be94</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>1626506410-20 - auxiliar de facturación - engativá</t>
+          <t>Auxiliar de facturacion // sector salud laboratorio clinico /// villavicencio meta</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="G18" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/162650641020-auxiliar-de-facturacion-engativa-1886768147", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-sector-salud-laboratorio-clinico-villavicencio-meta-1886746288", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>9211ddea62d9bfb6</t>
+          <t>6bf2402aaa779ade</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación experiencia en armado y radicación de cuentas</t>
+          <t>1626506410-20 - auxiliar de facturación - engativá</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>AGENCIA DE EMPLEO Y FOMENTO EMPRESARIAL COMPENSAR</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="G19" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-experiencia-en-armado-y-radicacion-de-cuentas-1886744224", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/162650641020-auxiliar-de-facturacion-engativa-1886768147", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
@@ -1408,7 +1408,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1525a4a624cf5cd3</t>
+          <t>9211ddea62d9bfb6</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion cuentas medicas indefinido</t>
+          <t>Auxiliar de facturación experiencia en armado y radicación de cuentas</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="G20" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-cuentas-medicas-indefinido-1886767336", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-experiencia-en-armado-y-radicacion-de-cuentas-1886744224", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H20" s="6" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>d24c0581ada3f712</t>
+          <t>1525a4a624cf5cd3</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Recepcionista auxiliar de facturación área laboratorio clínico</t>
+          <t>Auxiliar de facturacion cuentas medicas indefinido</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>MEDICALL TALENTO HUMANO S.A.S.</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="G21" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-auxiliar-de-facturacion-area-laboratorio-clinico-1886771966", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-cuentas-medicas-indefinido-1886767336", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>fb3dea6d6d65b76e</t>
+          <t>d24c0581ada3f712</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturacion conocimientos en sap</t>
+          <t>Recepcionista auxiliar de facturación área laboratorio clínico</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>ATIEMPO S.A.S</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="G22" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-conocimientos-en-sap-1886753956", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/recepcionista-auxiliar-de-facturacion-area-laboratorio-clinico-1886771966", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H22" s="6" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>88175481acb2458e</t>
+          <t>fb3dea6d6d65b76e</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Asistente contable y facturacion</t>
+          <t>Auxiliar de facturacion conocimientos en sap</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>ATIEMPO S.A.S</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="G23" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-facturacion-1886744516", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-conocimientos-en-sap-1886753956", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H23" s="6" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>d82065ac5307df49</t>
+          <t>88175481acb2458e</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Asistente contable y facturacion</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="G24" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886758187", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-contable-y-facturacion-1886744516", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25faa90c6ef28e21</t>
+          <t>d82065ac5307df49</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación e inventarios</t>
+          <t>Auxiliar de facturación</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Human construction sas</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="G25" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-e-inventarios-1886756606", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-1886758187", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H25" s="6" t="inlineStr"/>
@@ -1684,7 +1684,7 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>a40cdd7efd6dc67a</t>
+          <t>25faa90c6ef28e21</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación urgencias / hospitalizacion</t>
+          <t>Auxiliar de facturación e inventarios</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Fundación Santa Fe de Bogotá</t>
+          <t>Human construction sas</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="G26" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-hospitalizacion-1886752826", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-e-inventarios-1886756606", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H26" s="6" t="inlineStr"/>
@@ -1730,7 +1730,7 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>72196b37f0710891</t>
+          <t>a40cdd7efd6dc67a</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Asistente de operaciones y facturación</t>
+          <t>Auxiliar de facturación urgencias / hospitalizacion</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Fundación Santa Fe de Bogotá</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G27" s="5">
-        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/asistente-de-operaciones-y-facturacion-1886763278", "Ver Vacante")</f>
+        <f>HYPERLINK("https://www.elempleo.com/co/ofertas-trabajo/auxiliar-de-facturacion-urgencias-hospitalizacion-1886752826", "Ver Vacante")</f>
         <v/>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
@@ -1776,7 +1776,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>aa68d537158b69c9</t>
+          <t>72196b37f0710891</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar de facturación</t>
+          <t>Asistente de operaciones y facturación</t>
         </is>
       </c>
       <c r="D28" s=